--- a/pipeline/CASI_APERTI.xlsx
+++ b/pipeline/CASI_APERTI.xlsx
@@ -454,7 +454,9 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -476,7 +478,9 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -484,7 +488,9 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -492,7 +498,9 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -841,6 +849,7 @@
           <t>sed121|3|Bonomi</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -906,6 +915,7 @@
           <t>sed121|9|Pajetta. quanto</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1181,6 +1191,7 @@
           <t>sed129|16|Mastino</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1246,6 +1257,7 @@
           <t>sed129|19|Merlin</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1381,6 +1393,7 @@
           <t>sed130|2|Merlin</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1446,6 +1459,7 @@
           <t>sed130|8|Mastino</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1511,6 +1525,7 @@
           <t>sed130|9|Mastino</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1576,6 +1591,7 @@
           <t>sed189|3|Bonoini</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1711,6 +1727,7 @@
           <t>sed259|23|PerT</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1776,6 +1793,7 @@
           <t>sed261|10|Gullo</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1841,6 +1859,7 @@
           <t>sed283|18|Mastino</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1906,6 +1925,7 @@
           <t>sed301|6|Gullo</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1971,6 +1991,7 @@
           <t>sed301|7|Gullo</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2036,6 +2057,7 @@
           <t>sed308|4|Mastino</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2101,6 +2123,7 @@
           <t>sed308|10|Mastino</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2166,6 +2189,7 @@
           <t>sed308|11|Mastino</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2231,6 +2255,7 @@
           <t>sed309|6|CORTESE</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2296,6 +2321,7 @@
           <t>sed313|5|Mastino</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2361,6 +2387,7 @@
           <t>sed315|20|Gullo</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2426,6 +2453,7 @@
           <t>sed315|23|Gullo</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2491,6 +2519,7 @@
           <t>sed328|9|Cortese</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="28">
@@ -2619,7 +2648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2802,6 +2831,7 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>« Sostituire l'articolo 6 con il seguente: / « Lo Stato riconosce e garantisce l’autonomia, la libertà e la dignità della persona. umana come diritti inviolabili ed inhalieL'onorevole Rodinò ‘Mario ha facoltà di svolgerlo.</t>
@@ -2857,6 +2887,7 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
           <t>« Sostituire il secondo comma col seguente. / « È compito dello Stato rendere possibile id completo sviluppo della persona. umana 6 la partecipazione di tutti i cittadini all’orga. nizzazione economica e sociale della Nazione ». . / Chiedo all’onorevole Selvaggi se mantiene il suo emendamento. °</t>
@@ -2972,6 +3003,7 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>« Sostituire alle ultime parole della formulazione della Commissione: tra i popoli, le altre: tra le Nazioni »</t>
@@ -3087,6 +3119,7 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>«Tutti hanno diritto di professare liberamente la propria fede religiosa in qualsiasi forma, individuale o associata, di farne propaganda e di esercitare in privato ed in 'pubblico atti di culto, purhé non si tratti di riti contrari all'ordinamento giuridico dello Stato. / « Tutte le confessioni rel</t>
@@ -3142,6 +3175,7 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>«Sostituire i commi 3 e 4 coi seguenti ...»</t>
@@ -3197,6 +3231,7 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
           <t>nan</t>
@@ -3252,6 +3287,7 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
           <t>« L'arte: c la scienza sono libere e libero ne è l’insegnamento »</t>
@@ -3271,25 +3307,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sed117</t>
+          <t>sed105</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed117/sed117nc.pdf#page=4</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed105/sed105nc.pdf#page=13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed117.pdf, pagina 4</t>
+          <t>pipeline/pdf/sed105.pdf, pagina 13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Giannini Guglielmo, Maffioli Catullo</t>
+          <t>Silipo Luigi, Cortese Guido, Rodino' Di Miglione Mario, Lozza Stellio, Codignola Tristano, Marchesi Concetto, Bernini Ferdinando, Fabbri Gustavo, Badini Confalonieri Vittorio, Preti Luigi, Zagari Mario, Binni Walter, Corbino Epicarmo, Pacciardi Randolfo, Perrone Capano Giuseppe</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -3309,17 +3345,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>sed117 p2: «dall'onorevole Giannini e da altri colleghi»; p4: «Giannini, Maffioli ed altri» (lettura sull'immagine)</t>
+          <t>sed105 p13: «…Cortese, Perrone Capano e altri»; p14: «degli onorevoli Corbino, Marchesi ed altri»</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>« Gon decreto del Presidente del Consiglio dei Ministri, sentito. il parere della Commis:: sione ‘consultiva, potrà essere variato, di anno in anno, il numero delle giornate. da riservare ai film'nazionali, in relazione alla variazione delia «quantità t .qualità della produzione cinematografica nazi</t>
+          <t>« senza oneri per lo Stato »</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>sed117|4|d26060|d8980</t>
+          <t>sed105|13|d10410|d11340|d11480|d14030|d18330|d26320|d27300|d27800|d400|d4810|d6230|d6970|d7580|d9650|d9780</t>
         </is>
       </c>
     </row>
@@ -3331,25 +3367,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sed123</t>
+          <t>sed117</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed123/sed123nc.pdf#page=23</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed117/sed117nc.pdf#page=4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed123.pdf, pagina 23</t>
+          <t>pipeline/pdf/sed117.pdf, pagina 4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barbareschi Gaetano</t>
+          <t>Giannini Guglielmo, Maffioli Catullo</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -3367,14 +3403,19 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sed117 p2: «dall'onorevole Giannini e da altri colleghi»; p4: «Giannini, Maffioli ed altri» (lettura sull'immagine)</t>
+        </is>
+      </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>« Le successioni legittime e testamentarie . e le espropriazioni per motivi di interesse generale sono regolate per legge »</t>
+          <t>« Gon decreto del Presidente del Consiglio dei Ministri, sentito. il parere della Commis:: sione ‘consultiva, potrà essere variato, di anno in anno, il numero delle giornate. da riservare ai film'nazionali, in relazione alla variazione delia «quantità t .qualità della produzione cinematografica nazi</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>sed123|23|d27200</t>
+          <t>sed117|4|d26060|d8980</t>
         </is>
       </c>
     </row>
@@ -3386,25 +3427,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sed178</t>
+          <t>sed123</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed178/sed178nc.pdf#page=10</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed123/sed123nc.pdf#page=23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed178.pdf, pagina 10</t>
+          <t>pipeline/pdf/sed123.pdf, pagina 23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rescigno Matteo, Uberti Giovanni</t>
+          <t>Barbareschi Gaetano</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -3422,14 +3463,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>« Acque pubbliche ed energia elettrica, in quanto la loro regolamentazione non contrasti con la disciplina nazionale di'competenza dello Stato e con gli interessi di altre Regioni»</t>
+          <t>« Le successioni legittime e testamentarie . e le espropriazioni per motivi di interesse generale sono regolate per legge »</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>sed178|10|d10000|d28610</t>
+          <t>sed123|23|d27200</t>
         </is>
       </c>
     </row>
@@ -3441,25 +3483,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sed179</t>
+          <t>sed178</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed179/sed179nc.pdf#page=11</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed178/sed178nc.pdf#page=10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed179.pdf, pagina 11</t>
+          <t>pipeline/pdf/sed178.pdf, pagina 10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pesenti Antonio</t>
+          <t>Rescigno Matteo, Uberti Giovanni</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -3477,19 +3519,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>sed179 p11: «gli emendamenti dell'onorevole Pesenti e altri e dell'onorevole Dugoni», unificati dalla Commissione</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>«Agli stessi fini si considerano nel patrimonio del marito le azioni intestate a nome della moglie in occasione della nominatività obbligatoria dei titoli azionari, disposta dal regio decreto-legge 25 ottobre 1941, n. 1148, convertito nella legge 9 febbraio 1942, n.9»</t>
+          <t>« Acque pubbliche ed energia elettrica, in quanto la loro regolamentazione non contrasti con la disciplina nazionale di'competenza dello Stato e con gli interessi di altre Regioni»</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>sed179|11|d19570</t>
+          <t>sed178|10|d10000|d28610</t>
         </is>
       </c>
     </row>
@@ -3501,25 +3539,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sed180</t>
+          <t>sed179</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=2</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed179/sed179nc.pdf#page=11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed180.pdf, pagina 2</t>
+          <t>pipeline/pdf/sed179.pdf, pagina 11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carbonari Luigi, Pallastrelli Giovanni</t>
+          <t>Pesenti Antonio</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -3537,14 +3575,19 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>sed179 p11: «gli emendamenti dell'onorevole Pesenti e altri e dell'onorevole Dugoni», unificati dalla Commissione</t>
+        </is>
+      </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>« Dopo agricoltura e foreste, aggiungere: irrigazioni e miglioramenti agrari »</t>
+          <t>«Agli stessi fini si considerano nel patrimonio del marito le azioni intestate a nome della moglie in occasione della nominatività obbligatoria dei titoli azionari, disposta dal regio decreto-legge 25 ottobre 1941, n. 1148, convertito nella legge 9 febbraio 1942, n.9»</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>sed180|2|d27500|d28280</t>
+          <t>sed179|11|d19570</t>
         </is>
       </c>
     </row>
@@ -3556,25 +3599,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sed181</t>
+          <t>sed180</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed181/sed181nc.pdf#page=21</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed181.pdf, pagina 21</t>
+          <t>pipeline/pdf/sed180.pdf, pagina 2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rescigno Matteo, Carbonari Luigi</t>
+          <t>Carbonari Luigi, Pallastrelli Giovanni</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -3592,19 +3635,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>sed181 p21: «a firma degli onorevoli Carbonari, Rescigno ed altri colleghi»</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>« Aggiungere dopo il n. 80): / «I beni: immobili costituenti l'azienda agricola il cui reddito non superi il minimo di esistenza necessario per la famiglia del piccolo proprietario ». / Gli onorevoli Scoccimarro, Dugoni ed altri hanno poi presentato il seguente emendamento sostitutivo: . / « Sostitu</t>
+          <t>« Dopo agricoltura e foreste, aggiungere: irrigazioni e miglioramenti agrari »</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>sed181|21|d10000|d27500</t>
+          <t>sed180|2|d27500|d28280</t>
         </is>
       </c>
     </row>
@@ -3616,25 +3655,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sed183</t>
+          <t>sed181</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed183/sed183nc.pdf#page=30</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed181/sed181nc.pdf#page=21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed183.pdf, pagina 30</t>
+          <t>pipeline/pdf/sed181.pdf, pagina 21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Perugi Giulio, Cannizzo Bartolomeo, Marinaro Francesco, Bencivenga Roberto, Condorelli Orazio, Colitto Francesco, Corbino Epicarmo, Maffioli Catullo, Perrone Capano Giuseppe</t>
+          <t>Rescigno Matteo, Carbonari Luigi</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -3652,14 +3691,19 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>sed181 p21: «a firma degli onorevoli Carbonari, Rescigno ed altri colleghi»</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>« Fare del secondo comma un articolo a parte premettendo le seguenti parole: Nel caso di contribuenti, il cui patrimonio sia prevalentemente composto di valori mobiliari »</t>
+          <t>« Aggiungere dopo il n. 80): / «I beni: immobili costituenti l'azienda agricola il cui reddito non superi il minimo di esistenza necessario per la famiglia del piccolo proprietario ». / Gli onorevoli Scoccimarro, Dugoni ed altri hanno poi presentato il seguente emendamento sostitutivo: . / « Sostitu</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>sed183|30|d11960|d12000|d26340|d27260|d27630|d7550|d7580|d8980|d9780</t>
+          <t>sed181|21|d10000|d27500</t>
         </is>
       </c>
     </row>
@@ -3671,25 +3715,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sed189</t>
+          <t>sed183</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed189/sed189nc.pdf#page=18</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed183/sed183nc.pdf#page=30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed189.pdf, pagina 18</t>
+          <t>pipeline/pdf/sed183.pdf, pagina 30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arcaini Giuseppe, Scoca Salvatore, Cappi Giuseppe</t>
+          <t>Perugi Giulio, Cannizzo Bartolomeo, Marinaro Francesco, Bencivenga Roberto, Condorelli Orazio, Colitto Francesco, Corbino Epicarmo, Maffioli Catullo, Perrone Capano Giuseppe</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -3707,19 +3751,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>sed189 p18: presentato da Arcaini «anche a firma degli onorevoli Scoca, Cappi ed altri»</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>« AL secondo comma dell’articole 44, aggiungere le parole: nei confronti delle quali l’Amministrazione finanziaria ha però la facoltà di richiedere che l’Ispettorato del credito accerti la reale consistenza, alla data del 28 marzo 1947, dei debiti denunciati dal contribuente »</t>
+          <t>« Fare del secondo comma un articolo a parte premettendo le seguenti parole: Nel caso di contribuenti, il cui patrimonio sia prevalentemente composto di valori mobiliari »</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>sed189|18|d6490|d11760|d25470</t>
+          <t>sed183|30|d11960|d12000|d26340|d27260|d27630|d7550|d7580|d8980|d9780</t>
         </is>
       </c>
     </row>
@@ -3731,25 +3771,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sed192</t>
+          <t>sed189</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed192/sed192nc.pdf#page=23</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed189/sed189nc.pdf#page=18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed192.pdf, pagina 23</t>
+          <t>pipeline/pdf/sed189.pdf, pagina 18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rossi Paolo, Arata Giuseppe</t>
+          <t>Arcaini Giuseppe, Scoca Salvatore, Cappi Giuseppe</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -3767,14 +3807,19 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>sed189 p18: presentato da Arcaini «anche a firma degli onorevoli Scoca, Cappi ed altri»</t>
+        </is>
+      </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>« Alle parole: è punito con la multa da lire 10.000 a 5.000.000, sostituire le seguenti: è punito con la reclusione fino a 6 mesi e con la multa da lire 50.000 a 5.000.000 »</t>
+          <t>« AL secondo comma dell’articole 44, aggiungere le parole: nei confronti delle quali l’Amministrazione finanziaria ha però la facoltà di richiedere che l’Ispettorato del credito accerti la reale consistenza, alla data del 28 marzo 1947, dei debiti denunciati dal contribuente »</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>sed192|23|d10100|d6480</t>
+          <t>sed189|18|d6490|d11760|d25470</t>
         </is>
       </c>
     </row>
@@ -3786,25 +3831,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sed254</t>
+          <t>sed192</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed254/sed254nc.pdf#page=4</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed192/sed192nc.pdf#page=23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed254.pdf, pagina 4</t>
+          <t>pipeline/pdf/sed192.pdf, pagina 23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Benvenuti Lodovico Sforza, Bettiol Giuseppe Maria</t>
+          <t>Rossi Paolo, Arata Giuseppe</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -3822,14 +3867,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>« Contro la decisione di ciascuna Camera i deputati e i senatori possono ricorrere per ‘ violazione di legge alla Corte costituzionale »</t>
+          <t>« Alle parole: è punito con la multa da lire 10.000 a 5.000.000, sostituire le seguenti: è punito con la reclusione fino a 6 mesi e con la multa da lire 50.000 a 5.000.000 »</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>sed254|4|d11330|d17950</t>
+          <t>sed192|23|d10100|d6480</t>
         </is>
       </c>
     </row>
@@ -3841,25 +3887,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sed259</t>
+          <t>sed254</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed259/sed259nc.pdf#page=21</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed254/sed254nc.pdf#page=4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed259.pdf, pagina 21</t>
+          <t>pipeline/pdf/sed254.pdf, pagina 4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dominedo' Francesco Maria, Uberti Giovanni, Mortati Costantino</t>
+          <t>Benvenuti Lodovico Sforza, Bettiol Giuseppe Maria</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -3877,14 +3923,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>«Limitare l’articolo alle seguenti parole del primo comma: i disegni di legge approvati da una Camera sono trasmessi all'altra »</t>
+          <t>« Contro la decisione di ciascuna Camera i deputati e i senatori possono ricorrere per ‘ violazione di legge alla Corte costituzionale »</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>sed259|21|d25760|d28610|d9460</t>
+          <t>sed254|4|d11330|d17950</t>
         </is>
       </c>
     </row>
@@ -3896,25 +3943,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sed270</t>
+          <t>sed259</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed270/sed270nc.pdf#page=1</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed259/sed259nc.pdf#page=21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed270.pdf, pagina 1</t>
+          <t>pipeline/pdf/sed259.pdf, pagina 21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Laconi Renzo, Carboni Angelo</t>
+          <t>Dominedo' Francesco Maria, Uberti Giovanni, Mortati Costantino</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -3932,14 +3979,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>« Il Presidente della Repubblica 1504 | è eletto dall'Assemblea Nazionale con la par1501 | tecipazione di tre delegati per ogni Consiglio 1000 regionale eletti dal Consiglio, in modo che sia 1504 assicurata la rappresentanza della minoranza»</t>
+          <t>«Limitare l’articolo alle seguenti parole del primo comma: i disegni di legge approvati da una Camera sono trasmessi all'altra »</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>sed270|1|d11820|d7280</t>
+          <t>sed259|21|d25760|d28610|d9460</t>
         </is>
       </c>
     </row>
@@ -3955,21 +4003,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed270/sed270nc.pdf#page=14</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed270/sed270nc.pdf#page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed270.pdf, pagina 14</t>
+          <t>pipeline/pdf/sed270.pdf, pagina 1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La Rocca Vincenzo, Grieco Ruggero, Spano Velio</t>
+          <t>Laconi Renzo, Carboni Angelo</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -3987,14 +4035,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>« Il Governo della Repubblica è costituito dal Consiglio dei Ministri. / «I Ministri sono nominati dal Presidente della Repubblica ».</t>
+          <t>« Il Presidente della Repubblica 1504 | è eletto dall'Assemblea Nazionale con la par1501 | tecipazione di tre delegati per ogni Consiglio 1000 regionale eletti dal Consiglio, in modo che sia 1504 assicurata la rappresentanza della minoranza»</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>sed270|14|d11710|d28000|d28530</t>
+          <t>sed270|1|d11820|d7280</t>
         </is>
       </c>
     </row>
@@ -4006,25 +4055,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sed272</t>
+          <t>sed270</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed272/sed272nc.pdf#page=19</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed270/sed270nc.pdf#page=14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed272.pdf, pagina 19</t>
+          <t>pipeline/pdf/sed270.pdf, pagina 14</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Carpano Maglioli Ernesto</t>
+          <t>La Rocca Vincenzo, Grieco Ruggero, Spano Velio</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -4042,14 +4091,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>«non prima di un anno dalla loro elezione e nel caso che abbiano dato luogo a due mutamenti di Governo a seguito di voto di sfiducia nello spazio di un semestre »</t>
+          <t>« Il Governo della Repubblica è costituito dal Consiglio dei Ministri. / «I Ministri sono nominati dal Presidente della Repubblica ».</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>sed272|19|d11320</t>
+          <t>sed270|14|d11710|d28000|d28530</t>
         </is>
       </c>
     </row>
@@ -4061,25 +4111,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sed276</t>
+          <t>sed272</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed276/sed276nc.pdf#page=9</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed272/sed272nc.pdf#page=19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed276.pdf, pagina 9</t>
+          <t>pipeline/pdf/sed272.pdf, pagina 19</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rodi Cesario, Rodino' Di Miglione Mario, Bergamini Alberto, Condorelli Orazio, Colitto Francesco, Corbino Epicarmo, Perrone Capano Giuseppe</t>
+          <t>Carpano Maglioli Ernesto</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -4097,14 +4147,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>« È abrogata la disposizione di cui alla lettera f) del regio decreto 30 dicembre 1923, n. 2960, ed è sostituita con la seguente: / «Si incorre nella revoca dell’impiego per mancanza contro l’onore e per qualsiasi mancanza che dimostri difetto di senso morale ». / L'onorevole Condorelli ha già svolt</t>
+          <t>«non prima di un anno dalla loro elezione e nel caso che abbiano dato luogo a due mutamenti di Governo a seguito di voto di sfiducia nello spazio di un semestre »</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>sed276|9|d10050|d11480|d27280|d27630|d7550|d7580|d9780</t>
+          <t>sed272|19|d11320</t>
         </is>
       </c>
     </row>
@@ -4116,25 +4167,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sed300</t>
+          <t>sed276</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed300/sed300nc.pdf#page=2</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed276/sed276nc.pdf#page=9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed300.pdf, pagina 2</t>
+          <t>pipeline/pdf/sed276.pdf, pagina 9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Carpano Maglioli Ernesto, Colitto Francesco</t>
+          <t>Rodi Cesario, Rodino' Di Miglione Mario, Bergamini Alberto, Condorelli Orazio, Colitto Francesco, Corbino Epicarmo, Perrone Capano Giuseppe</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -4152,19 +4203,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>sed300 p2: «emendamento soppressivo degli onorevoli Colitto e Carpano Maglioli e altri»</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>«rappresentando un attentato alle libertà democratiche garantite dalla Costituzione »</t>
+          <t>« È abrogata la disposizione di cui alla lettera f) del regio decreto 30 dicembre 1923, n. 2960, ed è sostituita con la seguente: / «Si incorre nella revoca dell’impiego per mancanza contro l’onore e per qualsiasi mancanza che dimostri difetto di senso morale ». / L'onorevole Condorelli ha già svolt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>sed300|2|d11320|d7550</t>
+          <t>sed276|9|d10050|d11480|d27280|d27630|d7550|d7580|d9780</t>
         </is>
       </c>
     </row>
@@ -4176,25 +4223,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sed302</t>
+          <t>sed300</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed302/sed302nc.pdf#page=17</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed300/sed300nc.pdf#page=2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed302.pdf, pagina 17</t>
+          <t>pipeline/pdf/sed300.pdf, pagina 2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lussu Emilio, Mastino Pietro, Zanardi Francesco</t>
+          <t>Carpano Maglioli Ernesto, Colitto Francesco</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -4212,14 +4259,19 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>sed300 p2: «emendamento soppressivo degli onorevoli Colitto e Carpano Maglioli e altri»</t>
+        </is>
+      </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>«La legge regolerà i casi e le forme della ‘ partecipazione diretta del popolo alla amministrazione della giustizia »</t>
+          <t>«rappresentando un attentato alle libertà democratiche garantite dalla Costituzione »</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>sed302|17|d28070|d28150|d28680</t>
+          <t>sed300|2|d11320|d7550</t>
         </is>
       </c>
     </row>
@@ -4231,25 +4283,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sed303</t>
+          <t>sed302</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed303/sed303nc.pdf#page=18</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed302/sed302nc.pdf#page=17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed303.pdf, pagina 18</t>
+          <t>pipeline/pdf/sed302.pdf, pagina 17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clerici Edoardo, Mannironi Salvatore, Sansone Luigi Renato, Carboni Angelo, Mortati Costantino</t>
+          <t>Lussu Emilio, Mastino Pietro, Zanardi Francesco</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -4267,14 +4319,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>«Le sentenze della Corte di assise sono soggette ad appello nei modistabiliti dalla legge »</t>
+          <t>«La legge regolerà i casi e le forme della ‘ partecipazione diretta del popolo alla amministrazione della giustizia »</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>sed303|18|d14040|d26280|d26890|d7280|d9460</t>
+          <t>sed302|17|d28070|d28150|d28680</t>
         </is>
       </c>
     </row>
@@ -4286,25 +4339,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sed309</t>
+          <t>sed303</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed309/sed309nc.pdf#page=31</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed303/sed303nc.pdf#page=18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed309.pdf, pagina 31</t>
+          <t>pipeline/pdf/sed303.pdf, pagina 18</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Laconi Renzo, Mastino Gesumino, Murgia Francesco</t>
+          <t>Clerici Edoardo, Mannironi Salvatore, Sansone Luigi Renato, Carboni Angelo, Mortati Costantino</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -4322,14 +4375,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>«Le sentenze della Corte di assise sono soggette ad appello nei modistabiliti dalla legge »</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>sed309|31|d11820|d26390|d9490</t>
+          <t>sed303|18|d14040|d26280|d26890|d7280|d9460</t>
         </is>
       </c>
     </row>
@@ -4341,25 +4395,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sed311</t>
+          <t>sed309</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed311/sed311nc.pdf#page=28</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed309/sed309nc.pdf#page=31</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed311.pdf, pagina 28</t>
+          <t>pipeline/pdf/sed309.pdf, pagina 31</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lami Starnuti Edgardo</t>
+          <t>Laconi Renzo, Mastino Gesumino, Murgia Francesco</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -4377,14 +4431,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>«I giudici della Corte sono nominati dal Parlamento. »</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>sed311|28|d18990</t>
+          <t>sed309|31|d11820|d26390|d9490</t>
         </is>
       </c>
     </row>
@@ -4396,25 +4451,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sed317</t>
+          <t>sed311</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed317/sed317nc.pdf#page=13</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed311/sed311nc.pdf#page=28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed317.pdf, pagina 13</t>
+          <t>pipeline/pdf/sed311.pdf, pagina 28</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gullo Fausto, Laconi Renzo</t>
+          <t>Lami Starnuti Edgardo</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -4432,14 +4487,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>« Dopo le parole: diritti di libertà, aggiungere: e del lavoro »</t>
+          <t>«I giudici della Corte sono nominati dal Parlamento. »</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>sed317|13|d11230|d11820</t>
+          <t>sed311|28|d18990</t>
         </is>
       </c>
     </row>
@@ -4451,25 +4507,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sed318</t>
+          <t>sed317</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed318/sed318nc.pdf#page=14</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed317/sed317nc.pdf#page=13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed318.pdf, pagina 14</t>
+          <t>pipeline/pdf/sed317.pdf, pagina 13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Adonnino Giovan Battista</t>
+          <t>Gullo Fausto, Laconi Renzo</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -4487,14 +4543,15 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>« Dopo il terzo comma, aggiungere i seguenti: / «Ogni Regione, ove ritenga di impugnare un progetto di legge di altra Regione, per contrasto con i propri interessi, nel caso in cui il Governo abbia lasciato decdrrere il suddetto termine senza rinvio al Consiglio regionale, può proporre — nei success</t>
+          <t>« Dopo le parole: diritti di libertà, aggiungere: e del lavoro »</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>sed318|14|d11840</t>
+          <t>sed317|13|d11230|d11820</t>
         </is>
       </c>
     </row>
@@ -4506,25 +4563,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sed322</t>
+          <t>sed318</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed322/sed322nc.pdf#page=18</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed318/sed318nc.pdf#page=14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed322.pdf, pagina 18</t>
+          <t>pipeline/pdf/sed318.pdf, pagina 14</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Martino Gaetano</t>
+          <t>Adonnino Giovan Battista</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -4542,44 +4599,45 @@
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>«i deputati al Parlamento dichiarati decaduti nella seduta del 9 novembre 1926, che abbiano avuto tre o più legislature e siano stati chiamati a far parte della Consulta Nazionale »</t>
+          <t>« Dopo il terzo comma, aggiungere i seguenti: / «Ogni Regione, ove ritenga di impugnare un progetto di legge di altra Regione, per contrasto con i propri interessi, nel caso in cui il Governo abbia lasciato decdrrere il suddetto termine senza rinvio al Consiglio regionale, può proporre — nei success</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>sed322|18|d13430</t>
+          <t>sed318|14|d11840</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A012</t>
+          <t>A034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sed130</t>
+          <t>sed322</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed130/sed130nc.pdf#page=16</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed322/sed322nc.pdf#page=18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed130.pdf, pagina 16</t>
+          <t>pipeline/pdf/sed322.pdf, pagina 18</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Scoca Salvatore, Meda Luigi</t>
+          <t>Martino Gaetano</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -4594,52 +4652,48 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Grieco Ruggero; Laconi Renzo; Cremaschi Carlo</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>elenco completo stampato nella seduta (lettura sull'immagine)</t>
-        </is>
-      </c>
+          <t>nessun elenco completo stampato</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>«i deputati al Parlamento dichiarati decaduti nella seduta del 9 novembre 1926, che abbiano avuto tre o più legislature e siano stati chiamati a far parte della Consulta Nazionale »</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>sed130|16|d11760|d12410</t>
+          <t>sed322|18|d13430</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A016</t>
+          <t>A012</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sed180</t>
+          <t>sed130</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=15</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed130/sed130nc.pdf#page=16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed180.pdf, pagina 15</t>
+          <t>pipeline/pdf/sed130.pdf, pagina 16</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Giua Michele, Jacometti Alberto</t>
+          <t>Scoca Salvatore, Meda Luigi</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -4654,7 +4708,7 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Amadei Leonetto; Malagugini Alcide; Bernini Ferdinando</t>
+          <t>Grieco Ruggero; Laconi Renzo; Cremaschi Carlo</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4664,42 +4718,42 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>«Si debbono ora esaminare le proposte di alinea aggiuntivi a quelli elencati dalla Commissione. / Vi è un emendamento dell’onorevole Perassi ed altri che propongono di aggiungere: « Artigianato, industria e commercio ». / L'onorevole .Zuccarini, da parte sua, propone di aggiungere un alinea così for</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>sed180|15|d27970|d8770</t>
+          <t>sed130|16|d11760|d12410</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A019</t>
+          <t>A016</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sed186</t>
+          <t>sed180</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed186/sed186nc.pdf#page=18</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed186.pdf, pagina 18</t>
+          <t>pipeline/pdf/sed180.pdf, pagina 15</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nobile Umberto, Porzio Giovanni, Di Gloria Calogero, Persico Giovanni, Bernini Ferdinando, Veroni Dante, Morelli Renato, Gasparotto Luigi, Lami Starnuti Edgardo, Corsi Angelo, Finocchiaro Aprile Andrea, Giannini Guglielmo, Massini Cesare</t>
+          <t>Giua Michele, Jacometti Alberto</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -4714,52 +4768,52 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>elenco già completo</t>
+          <t>Amadei Leonetto; Malagugini Alcide; Bernini Ferdinando</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>nessun «ed altri» stampato dopo i 13 nomi (lettura sull'immagine)</t>
+          <t>elenco completo stampato nella seduta (lettura sull'immagine)</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>« Aggiungere, in fine, il seguente comma: / «La Regione non può in alcun modo limitare il diritto dei cittadini ad esercitare, in _ qualunque parte del territorio nazionale paia ad essi conveniente, la loro arte, professione o mestiere ».</t>
+          <t>«Si debbono ora esaminare le proposte di alinea aggiuntivi a quelli elencati dalla Commissione. / Vi è un emendamento dell’onorevole Perassi ed altri che propongono di aggiungere: « Artigianato, industria e commercio ». / L'onorevole .Zuccarini, da parte sua, propone di aggiungere un alinea così for</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>sed186|18|d9610|d28370|d17310|d28340|d27300|d28650|d9440|d27920|d18990|d13130|d25900|d26060|d28140</t>
+          <t>sed180|15|d27970|d8770</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A035</t>
+          <t>A019</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sed319</t>
+          <t>sed186</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed319/sed319nc.pdf#page=21</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed186/sed186nc.pdf#page=18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed319.pdf, pagina 21</t>
+          <t>pipeline/pdf/sed186.pdf, pagina 18</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cifaldi Antonio, Nobile Umberto</t>
+          <t>Nobile Umberto, Porzio Giovanni, Di Gloria Calogero, Persico Giovanni, Bernini Ferdinando, Veroni Dante, Morelli Renato, Gasparotto Luigi, Lami Starnuti Edgardo, Corsi Angelo, Finocchiaro Aprile Andrea, Giannini Guglielmo, Massini Cesare</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -4774,87 +4828,147 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Grieco Ruggero; Nobili Tito Oro; Costa Gastone; Costantini Antonio</t>
+          <t>elenco già completo</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>elenco completo ristampato in sed321 p34</t>
+          <t>nessun «ed altri» stampato dopo i 13 nomi (lettura sull'immagine)</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>« Nessuna variazione al numero e alle circoscrizioni delle Regioni quali sono definite nell’articolo 123 potrà essere apportata nei primi dieci anni dopo la promulgazione della Costituzione »</t>
+          <t>« Aggiungere, in fine, il seguente comma: / «La Regione non può in alcun modo limitare il diritto dei cittadini ad esercitare, in _ qualunque parte del territorio nazionale paia ad essi conveniente, la loro arte, professione o mestiere ».</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>sed319|21|d25590|d9610</t>
+          <t>sed186|18|d9610|d28370|d17310|d28340|d27300|d28650|d9440|d27920|d18990|d13130|d25900|d26060|d28140</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>A035</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sed319</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>21</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed319/sed319nc.pdf#page=21</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>pipeline/pdf/sed319.pdf, pagina 21</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Cifaldi Antonio, Nobile Umberto</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>L'elenco è chiuso da «ed altri». Cerca nella stessa seduta o nelle vicine se lo stesso emendamento è stampato con tutte le firme (spesso il Presidente lo rilegge prima del voto). Se le trovi, scrivi in DECISIONE i nomi mancanti separati da punto e virgola, come «Rossi Paolo; Corsi»; altrimenti scegli «nessun elenco completo stampato».</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>nessun elenco completo stampato | &lt;nomi separati da ;&gt;</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Grieco Ruggero; Nobili Tito Oro; Costa Gastone; Costantini Antonio</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>elenco completo ristampato in sed321 p34</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>« Nessuna variazione al numero e alle circoscrizioni delle Regioni quali sono definite nell’articolo 123 potrà essere apportata nei primi dieci anni dopo la promulgazione della Costituzione »</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>sed319|21|d25590|d9610</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>A017</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>sed189</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C40" t="n">
         <v>18</v>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed189/sed189nc.pdf#page=18</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>pipeline/pdf/sed189.pdf, pagina 18</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Scoca Salvatore, Cappi Giuseppe</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>L'elenco è chiuso da «ed altri». Cerca nella stessa seduta o nelle vicine se lo stesso emendamento è stampato con tutte le firme (spesso il Presidente lo rilegge prima del voto). Se le trovi, scrivi in DECISIONE i nomi mancanti separati da punto e virgola, come «Rossi Paolo; Corsi»; altrimenti scegli «nessun elenco completo stampato».</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>nessun elenco completo stampato | &lt;nomi separati da ;&gt;</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>nessun elenco completo stampato</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>sed189 p18: presentato da Arcaini «anche a firma degli onorevoli Scoca, Cappi ed altri»; Arcaini aggiunto come presentatore in FIRMATARI_CORRETTI</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>« AL secondo comma dell’articole 44, aggiungere le parole: nei confronti delle quali l’Amministrazione finanziaria ha però la facoltà di richiedere che l’Ispettorato del credito accerti la reale consistenza, alla data del 28 marzo 1947, dei debiti denunciati dal contribuente »</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>sed189|18|d11760|d25470</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="38">
+  <dataValidations count="39">
     <dataValidation sqref="I2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"nessun elenco completo stampato"</formula1>
     </dataValidation>
@@ -4967,6 +5081,9 @@
       <formula1>"nessun elenco completo stampato"</formula1>
     </dataValidation>
     <dataValidation sqref="I39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"nessun elenco completo stampato"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"nessun elenco completo stampato"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5009,6 +5126,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5020,7 +5138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5138,7 +5256,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>VANNI</t>
+          <t>GIEVANNI</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5153,7 +5271,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Vanoni Ezio | Avanzini Ennio | Villani Ezio | Valiani Leo | Valenti Michele | Taviani Paolo Emilio | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Di Giovanni Eduardo | Giannini Guglielmo | Vanoni Ezio | Gervasi Galliano | Castrogiovanni Attilio | Giordani Igino | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -5161,9 +5279,14 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>coda di «Farina Gio-vanni», già contato</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>sed084|4|sì|VANNI|0</t>
+          <t>sed084|4|sì|GIEVANNI|0</t>
         </is>
       </c>
     </row>
@@ -5175,37 +5298,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>v4</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>congedo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sed084</t>
+          <t>sed086</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed084/sed084nc.pdf#page=4</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed086/sed086nc.pdf#page=17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed084.pdf, dalla pagina 4 (elenco del «no»)</t>
+          <t>pipeline/pdf/sed086.pdf, dalla pagina 17 (elenco del «congedo»)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FEDE</t>
+          <t>CGARPANO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FANFANI … FERRARIO CELESTINO</t>
+          <t>CACCIATORE … CINGOLANI</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -5215,17 +5338,18 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Fantoni Luciano | Faralli Vannuccio | Fedeli Aldo | Fedeli Armando | Federici Maria | Ferrarese Antonio | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Scarpa Sergio | Germano Attilio | Garlato Giuseppe | Carmagnola Luigi | Caprani Aldo | Chatrian Luigi | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Federici Maria</t>
-        </is>
-      </c>
+          <t>Carpano Maglioli Ernesto</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>sed084|4|no|FEDE|0</t>
+          <t>sed086|17|congedo|CGARPANO|0</t>
         </is>
       </c>
     </row>
@@ -5237,37 +5361,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>v6</t>
+          <t>v8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>congedo</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sed086</t>
+          <t>sed102</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed086/sed086nc.pdf#page=17</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed086.pdf, dalla pagina 17 (elenco del «congedo»)</t>
+          <t>pipeline/pdf/sed102.pdf, dalla pagina 16 (elenco del «sì»)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CGARPANO</t>
+          <t>NATO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CACCIATORE … CINGOLANI</t>
+          <t>MORELLI … MORINI</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -5277,17 +5401,18 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Scarpa Sergio | Germano Attilio | Garlato Giuseppe | Carmagnola Luigi | Caprani Aldo | Chatrian Luigi | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Morelli Luigi | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Carpano Maglioli Ernesto</t>
-        </is>
-      </c>
+          <t>nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>sed086|17|congedo|CGARPANO|0</t>
+          <t>sed102|16|sì|NATO|0</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5429,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>congedo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5319,17 +5444,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed102.pdf, dalla pagina 16 (elenco del «sì»)</t>
+          <t>pipeline/pdf/sed102.pdf, dalla pagina 16 (elenco del «congedo»)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NATO</t>
+          <t>BRAGAGNA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MORELLI … MORINI</t>
+          <t>BERNARDI … CAROLEO</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -5339,7 +5464,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Morelli Luigi | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Bertini Giovanni | Biagioni Loris | Bianchi Costante | Binni Walter | Boldrini Arrigo | Bolognesi Severino | Bonfantini Corrado | Bonino Uberto | Borsellino Raimondo Salvatore | Buffoni Francesco | Buonocore Giuseppe | Cacciatore Luigi | Campilli Pietro | Cannizzo Bartolomeo | Cappa Paolo | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -5347,9 +5472,14 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>elenco dei congedi, non è un voto</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>sed102|16|sì|NATO|0</t>
+          <t>sed102|16|congedo|BRAGAGNA|0</t>
         </is>
       </c>
     </row>
@@ -5409,6 +5539,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>sed104|21|no|ARMARALI|0</t>
@@ -5423,7 +5554,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>v13</t>
+          <t>v12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5433,27 +5564,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sed129</t>
+          <t>sed105</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed129/sed129nc.pdf#page=35</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed105/sed105nc.pdf#page=15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed129.pdf, dalla pagina 35 (elenco del «no»)</t>
+          <t>pipeline/pdf/sed105.pdf, dalla pagina 15 (elenco del «no»)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>WTRR</t>
+          <t>RRRR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CRISPO … DAMICO DIEGO</t>
+          <t>CREMASCHI CARLO … DAMICO DIEGO</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -5463,7 +5594,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Croce Benedetto | Cuomo Giovanni | D'Amico Michele | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Crispo Amerigo | Croce Benedetto | Cuomo Giovanni | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -5471,9 +5602,14 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>rumore OCR</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>sed129|35|no|WTRR|0</t>
+          <t>sed105|15|no|RRRR|0</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5646,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ASTENULI</t>
+          <t>WTRR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ZOTTA … MORO</t>
+          <t>CRISPO … DAMICO DIEGO</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -5525,7 +5661,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Castelli Edgardo | Segni Antonio | Pallastrelli Giovanni | Lami Starnuti Edgardo | Castiglia Pietro | Trulli Martino | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Croce Benedetto | Cuomo Giovanni | D'Amico Michele | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -5533,9 +5669,10 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>sed129|35|no|ASTENULI|0</t>
+          <t>sed129|35|no|WTRR|0</t>
         </is>
       </c>
     </row>
@@ -5595,6 +5732,7 @@
           <t>Cartia Giovanni</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>sed177|17|sì|GARTIIA|0</t>
@@ -5657,6 +5795,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>sed177|17|sì|AUGIOLA|0</t>
@@ -5719,6 +5858,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>sed178|16|congedo|PULTO|0</t>
@@ -5781,6 +5921,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>sed180|16|sì|EISABETTA|0</t>
@@ -5843,6 +5984,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>sed180|16|sì|OOIOIZAII|0</t>
@@ -5905,6 +6047,7 @@
           <t>Gullo Rocco</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>sed180|16|congedo|GUILO|0</t>
@@ -6034,6 +6177,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>sed188|15|sì|MANA|0</t>
@@ -6096,6 +6240,7 @@
           <t>Amadei Leonetto</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>sed260|13|sì|AIIADEI|0</t>
@@ -6158,6 +6303,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>sed260|13|no|LAMII|0</t>
@@ -6220,6 +6366,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>sed270|18|sì|MONTI|0</t>
@@ -6282,6 +6429,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>sed270|18|no|NATIA|0</t>
@@ -6344,6 +6492,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>sed270|18|no|ACATIVLETZZTTI|0</t>
@@ -6406,6 +6555,7 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>sed270|18|no|DONIZETTI|0</t>
@@ -6468,6 +6618,7 @@
           <t>Guerrieri Filippo</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>sed277|7|no|GUERW|0</t>
@@ -6507,12 +6658,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CUPANO</t>
+          <t>OPRM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PERRONE … PERUGI</t>
+          <t>GUERRIERI EMANUELE … GUI</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -6522,7 +6673,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Pertini Alessandro | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Guerrieri Filippo | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -6530,9 +6681,14 @@
           <t>nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>rumore OCR</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>sed277|7|no|CUPANO|0</t>
+          <t>sed277|7|no|OPRM|0</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6700,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>v25</t>
+          <t>v24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6554,27 +6710,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sed296</t>
+          <t>sed277</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed296/sed296nc.pdf#page=27</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed277/sed277nc.pdf#page=7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed296.pdf, dalla pagina 27 (elenco del «no»)</t>
+          <t>pipeline/pdf/sed277.pdf, dalla pagina 7 (elenco del «no»)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BARONTINI</t>
+          <t>CUPANO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>BARGAGNA … BARTALINI</t>
+          <t>PERRONE … PERUGI</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -6584,17 +6740,18 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Barontini Anelito | Barontini Ilio | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Pertini Alessandro | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Barontini Ilio</t>
-        </is>
-      </c>
+          <t>nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>sed296|27|no|BARONTINI|0</t>
+          <t>sed277|7|no|CUPANO|0</t>
         </is>
       </c>
     </row>
@@ -6606,37 +6763,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>v26</t>
+          <t>v25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>sed301</t>
+          <t>sed296</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed301/sed301nc.pdf#page=7</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed296/sed296nc.pdf#page=27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed301.pdf, dalla pagina 7 (elenco del «sì»)</t>
+          <t>pipeline/pdf/sed296.pdf, dalla pagina 27 (elenco del «no»)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PAULO</t>
+          <t>BARONTINI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DE MICHELIS … DE VITA</t>
+          <t>BARGAGNA … BARTALINI</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -6646,17 +6803,18 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Sullo Fiorentino | Spano Velio | Puoti Renato | Gullo Fausto | Gullo Rocco | Gullo Fausto | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Barontini Anelito | Barontini Ilio | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>nessuno (rumore OCR / non è un costituente)</t>
-        </is>
-      </c>
+          <t>Barontini Ilio</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>sed301|7|sì|PAULO|0</t>
+          <t>sed296|27|no|BARONTINI|0</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6831,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6688,17 +6846,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed301.pdf, dalla pagina 7 (elenco del «no»)</t>
+          <t>pipeline/pdf/sed301.pdf, dalla pagina 7 (elenco del «sì»)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GARO</t>
+          <t>PAULO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DAMIANI … DE GASPERI</t>
+          <t>DE MICHELIS … DE VITA</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -6708,17 +6866,18 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>D'Aragona Lodovico | De Caro Gerardo | De Falco Giuseppe | De Filpo Luigi | nessuno (rumore OCR / non è un costituente)</t>
+          <t>Sullo Fiorentino | Spano Velio | Puoti Renato | Gullo Fausto | Gullo Rocco | Gullo Fausto | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>De Caro Gerardo</t>
-        </is>
-      </c>
+          <t>nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>sed301|7|no|GARO|0</t>
+          <t>sed301|7|sì|PAULO|0</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6889,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>v27</t>
+          <t>v26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6740,27 +6899,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>sed311</t>
+          <t>sed301</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed311/sed311nc.pdf#page=29</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed301/sed301nc.pdf#page=7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>pipeline/pdf/sed311.pdf, dalla pagina 29 (elenco del «no»)</t>
+          <t>pipeline/pdf/sed301.pdf, dalla pagina 7 (elenco del «no»)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MESTINO</t>
+          <t>GARO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MASTINO GESUMINO … MAZZA</t>
+          <t>DAMIANI … DE GASPERI</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -6770,17 +6929,18 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Mastino Pietro | Mattarella Bernardo | Matteotti Giancarlo | Matteotti Gianmatteo | nessuno (rumore OCR / non è un costituente)</t>
+          <t>D'Aragona Lodovico | De Caro Gerardo | De Falco Giuseppe | De Filpo Luigi | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>Mastino Pietro</t>
-        </is>
-      </c>
+          <t>De Caro Gerardo</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>sed311|29|no|MESTINO|0</t>
+          <t>sed301|7|no|GARO|0</t>
         </is>
       </c>
     </row>
@@ -6792,82 +6952,328 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>v27</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sed311</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed311/sed311nc.pdf#page=29</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>pipeline/pdf/sed311.pdf, dalla pagina 29 (elenco del «no»)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MESTINO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>MASTINO GESUMINO … MAZZA</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Trova il nome nell'elenco stampato del voto indicato (è in ordine alfabetico, fra i due nomi della colonna «tra»). Scegli il costituente; «nessuno» se è una parola del verbale o un pezzo di un nome già contato.</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Mastino Pietro | Mattarella Bernardo | Matteotti Giancarlo | Matteotti Gianmatteo | nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Mastino Pietro</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>sed311|29|no|MESTINO|0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>V001</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sed084</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed084/sed084nc.pdf#page=4</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pipeline/pdf/sed084.pdf, dalla pagina 4 (elenco del «sì»)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>VANNI</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>FARINA … FARINI CARLO</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Trova il nome nell'elenco stampato del voto indicato (è in ordine alfabetico, fra i due nomi della colonna «tra»). Scegli il costituente; «nessuno» se è una parola del verbale o un pezzo di un nome già contato.</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Vanoni Ezio | Avanzini Ennio | Villani Ezio | Valiani Leo | Valenti Michele | Taviani Paolo Emilio | nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>sed084|4|sì|VANNI|0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>V002</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>sed084</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed084/sed084nc.pdf#page=4</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>pipeline/pdf/sed084.pdf, dalla pagina 4 (elenco del «no»)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>FEDE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>FANFANI … FERRARIO CELESTINO</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Trova il nome nell'elenco stampato del voto indicato (è in ordine alfabetico, fra i due nomi della colonna «tra»). Scegli il costituente; «nessuno» se è una parola del verbale o un pezzo di un nome già contato.</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Fantoni Luciano | Faralli Vannuccio | Fedeli Aldo | Fedeli Armando | Federici Maria | Ferrarese Antonio | nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Federici Maria</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>sed084|4|no|FEDE|0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>V007</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>v13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sed129</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed129/sed129nc.pdf#page=35</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>pipeline/pdf/sed129.pdf, dalla pagina 35 (elenco del «no»)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ASTENULI</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ZOTTA … MORO</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Trova il nome nell'elenco stampato del voto indicato (è in ordine alfabetico, fra i due nomi della colonna «tra»). Scegli il costituente; «nessuno» se è una parola del verbale o un pezzo di un nome già contato.</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Castelli Edgardo | Segni Antonio | Pallastrelli Giovanni | Lami Starnuti Edgardo | Castiglia Pietro | Trulli Martino | nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>nessuno (rumore OCR / non è un costituente)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>sed129|35|no|ASTENULI|0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>V028</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>v28</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>sed315</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed315/sed315nc.pdf#page=25</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>pipeline/pdf/sed315.pdf, dalla pagina 25 (elenco del «sì»)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>GOLOM</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>CARPANO MAGLIOLI … COSTA</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Trova il nome nell'elenco stampato del voto indicato (è in ordine alfabetico, fra i due nomi della colonna «tra»). Scegli il costituente; «nessuno» se è una parola del verbale o un pezzo di un nome già contato.</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>Colombo Emilio | Colombi Arturo Raffaello | Gullo Fausto | Gullo Rocco | Gullo Fausto | Gullo Rocco | nessuno (rumore OCR / non è un costituente)</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Colombi Arturo Raffaello</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>sed315|25|sì|GOLOM|0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="27">
+  <dataValidations count="30">
     <dataValidation sqref="K2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Vanoni Ezio,Avanzini Ennio,Villani Ezio,Valiani Leo,Valenti Michele,Taviani Paolo Emilio,nessuno (rumore OCR / non è un costituente)"</formula1>
+      <formula1>"Di Giovanni Eduardo,Giannini Guglielmo,Vanoni Ezio,Gervasi Galliano,Castrogiovanni Attilio,Giordani Igino,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
     <dataValidation sqref="K3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Fantoni Luciano,Faralli Vannuccio,Fedeli Aldo,Fedeli Armando,Federici Maria,Ferrarese Antonio,nessuno (rumore OCR / non è un costituente)"</formula1>
+      <formula1>"Scarpa Sergio,Germano Attilio,Garlato Giuseppe,Carmagnola Luigi,Caprani Aldo,Chatrian Luigi,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
     <dataValidation sqref="K4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Scarpa Sergio,Germano Attilio,Garlato Giuseppe,Carmagnola Luigi,Caprani Aldo,Chatrian Luigi,nessuno (rumore OCR / non è un costituente)"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Morelli Luigi,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
     <dataValidation sqref="K6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Faralli Vannuccio,Carratelli Benedetto,Macrelli Gino,Caporali Giovanni Ernesto,Parri Ferruccio,Valmarana Giustino,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
     <dataValidation sqref="K7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Crispo Amerigo,Croce Benedetto,Cuomo Giovanni,nessuno (rumore OCR / non è un costituente)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Croce Benedetto,Cuomo Giovanni,D'Amico Michele,nessuno (rumore OCR / non è un costituente)"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Castelli Edgardo,Segni Antonio,Pallastrelli Giovanni,Lami Starnuti Edgardo,Castiglia Pietro,Trulli Martino,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
     <dataValidation sqref="K9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Cartia Giovanni,Caso Giovanni,Cassiani Gennaro,Castelli Edgardo,Castiglia Pietro,Castrogiovanni Attilio,Cavallari Vincenzo,Cavalli Antonio,Cavallotti Alberto Mario,Cerreti Giulio,nessuno (rumore OCR / non è un costituente)"</formula1>
@@ -6912,21 +7318,33 @@
       <formula1>"Guerrieri Filippo,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
     <dataValidation sqref="K24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Guerrieri Filippo,nessuno (rumore OCR / non è un costituente)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pertini Alessandro,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
-    <dataValidation sqref="K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Barontini Anelito,Barontini Ilio,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
-    <dataValidation sqref="K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sullo Fiorentino,Spano Velio,Puoti Renato,Gullo Fausto,Gullo Rocco,Gullo Fausto,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
-    <dataValidation sqref="K27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"D'Aragona Lodovico,De Caro Gerardo,De Falco Giuseppe,De Filpo Luigi,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
-    <dataValidation sqref="K28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Mastino Pietro,Mattarella Bernardo,Matteotti Giancarlo,Matteotti Gianmatteo,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
-    <dataValidation sqref="K29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Vanoni Ezio,Avanzini Ennio,Villani Ezio,Valiani Leo,Valenti Michele,Taviani Paolo Emilio,nessuno (rumore OCR / non è un costituente)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Fantoni Luciano,Faralli Vannuccio,Fedeli Aldo,Fedeli Armando,Federici Maria,Ferrarese Antonio,nessuno (rumore OCR / non è un costituente)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Castelli Edgardo,Segni Antonio,Pallastrelli Giovanni,Lami Starnuti Edgardo,Castiglia Pietro,Trulli Martino,nessuno (rumore OCR / non è un costituente)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Colombo Emilio,Colombi Arturo Raffaello,Gullo Fausto,Gullo Rocco,Gullo Fausto,Gullo Rocco,nessuno (rumore OCR / non è un costituente)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6959,6 +7377,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6970,7 +7392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7122,6 +7544,7 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>sed072|16|sì|RUGSIERO|d10130</t>
@@ -7189,6 +7612,7 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>sed072|16|no|TIER|d12480</t>
@@ -7256,6 +7680,7 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>sed072|16|no|VIGU|d20330</t>
@@ -7323,6 +7748,7 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>sed073|20|sì|ROSSI|d28430</t>
@@ -7390,6 +7816,7 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>sed073|20|no|CINGOLANII|d27610</t>
@@ -7457,6 +7884,7 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>sed073|20|no|RONMNIANO|d28420</t>
@@ -7524,6 +7952,7 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>sed075|50|sì|AYROLDI|d27160</t>
@@ -7591,6 +8020,7 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>sed075|50|sì|CAROLED|d13010</t>
@@ -7625,22 +8055,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COLONNA</t>
+          <t>ORLANDO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Colonna Di Paliano Carlo</t>
+          <t>Orlando Vittorio Emanuele</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>omonimo risolto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COLOMBO EMILIO … COLONNETTI</t>
+          <t>ORLANDO CAMILLO … PAJETTA GIAN CARLO</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -7658,9 +8088,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>sed075|50|sì|COLONNA|d18390</t>
+          <t>sed075|50|sì|ORLANDO|d28270</t>
         </is>
       </c>
     </row>
@@ -7692,22 +8123,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CURTO</t>
+          <t>ROMANQ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Del Curto Giovanni</t>
+          <t>Romano Antonio</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DE GASPERI … DELLI CASTELLI FILOMENA</t>
+          <t>RODINO MARIO … ROSELLI</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -7725,9 +8156,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>sed075|50|sì|CURTO|d27750</t>
+          <t>sed075|50|sì|ROMANQ|d28420</t>
         </is>
       </c>
     </row>
@@ -7759,22 +8191,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ORLANDO</t>
+          <t>TETRANOVA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Orlando Vittorio Emanuele</t>
+          <t>Terranova Corrado</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>omonimo risolto</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ORLANDO CAMILLO … PAJETTA GIAN CARLO</t>
+          <t>TAVIANI … TESSITORI</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -7792,9 +8224,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>sed075|50|sì|ORLANDO|d28270</t>
+          <t>sed075|50|sì|TETRANOVA|d13480</t>
         </is>
       </c>
     </row>
@@ -7811,7 +8244,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7826,22 +8259,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ROMANQ</t>
+          <t>CARIEPA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Romano Antonio</t>
+          <t>Canepa Giuseppe</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>RODINO MARIO … ROSELLI</t>
+          <t>CANDELA … CANEVARI</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -7859,9 +8292,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>sed075|50|sì|ROMANQ|d28420</t>
+          <t>sed075|50|no|CARIEPA|d27460</t>
         </is>
       </c>
     </row>
@@ -7878,7 +8312,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7893,12 +8327,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TETRANOVA</t>
+          <t>CHIARAMELIO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Terranova Corrado</t>
+          <t>Chiaramello Domenico</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -7908,7 +8342,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TAVIANI … TESSITORI</t>
+          <t>CEVOLOTTO … CHIOSTERGI</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -7926,9 +8360,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>sed075|50|sì|TETRANOVA|d13480</t>
+          <t>sed075|50|no|CHIARAMELIO|d7460</t>
         </is>
       </c>
     </row>
@@ -7960,22 +8395,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CARIEPA</t>
+          <t>SANSENE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Canepa Giuseppe</t>
+          <t>Sansone Luigi Renato</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CANDELA … CANEVARI</t>
+          <t>SALERNO … SANTI</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -7993,9 +8428,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>sed075|50|no|CARIEPA|d27460</t>
+          <t>sed075|50|no|SANSENE|d26890</t>
         </is>
       </c>
     </row>
@@ -8007,32 +8443,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sed075</t>
+          <t>sed084</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed075/sed075nc.pdf#page=50</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed084/sed084nc.pdf#page=4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CHIARAMELIO</t>
+          <t>CERRETTI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chiaramello Domenico</t>
+          <t>Cerreti Giulio</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -8042,7 +8478,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CEVOLOTTO … CHIOSTERGI</t>
+          <t>CAVALLARI … CEVOLOTTO</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -8060,9 +8496,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>sed075|50|no|CHIARAMELIO|d7460</t>
+          <t>sed084|4|sì|CERRETTI|d18180</t>
         </is>
       </c>
     </row>
@@ -8074,32 +8511,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>sed075</t>
+          <t>sed084</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed075/sed075nc.pdf#page=50</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed084/sed084nc.pdf#page=4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANSENE</t>
+          <t>GESTANTINI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sansone Luigi Renato</t>
+          <t>Costantini Antonio</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -8109,7 +8546,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SALERNO … SANTI</t>
+          <t>COSTA … CREMASCHI OLINDO</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -8127,9 +8564,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>sed075|50|no|SANSENE|d26890</t>
+          <t>sed084|4|sì|GESTANTINI|d27690</t>
         </is>
       </c>
     </row>
@@ -8161,12 +8599,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CERRETTI</t>
+          <t>RUGGIERI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cerreti Giulio</t>
+          <t>Ruggeri Luigi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -8176,7 +8614,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CAVALLARI … CEVOLOTTO</t>
+          <t>ROVEDA … SCHIAVETTI</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -8194,9 +8632,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>sed084|4|sì|CERRETTI|d18180</t>
+          <t>sed084|4|sì|RUGGIERI|d19820</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8652,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8228,12 +8667,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GESTANTINI</t>
+          <t>LUMMINELLI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Costantini Antonio</t>
+          <t>Tumminelli Michele Maria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -8243,7 +8682,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COSTA … CREMASCHI OLINDO</t>
+          <t>TREVES … TUPINI</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -8261,9 +8700,14 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lettura dell'immagine: «Tumminelli» fra Treves e Tupini</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>sed084|4|sì|GESTANTINI|d27690</t>
+          <t>sed084|4|no|LUMMINELLI|d10690</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8724,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8295,12 +8739,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RUGGIERI</t>
+          <t>VILARD</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ruggeri Luigi</t>
+          <t>Vilardi Giuseppe</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -8310,7 +8754,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ROVEDA … SCHIAVETTI</t>
+          <t>VICENTINI … ZERBI</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -8328,9 +8772,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>sed084|4|sì|RUGGIERI|d19820</t>
+          <t>sed084|4|no|VILARD|d28660</t>
         </is>
       </c>
     </row>
@@ -8342,12 +8787,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>v4</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8357,17 +8802,17 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed084/sed084nc.pdf#page=4</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed084/sed084nc.pdf#page=13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VILARD</t>
+          <t>LOPARDII</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Vilardi Giuseppe</t>
+          <t>Lopardi Emidio</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -8377,7 +8822,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VICENTINI … ZERBI</t>
+          <t>LOMBARDI RICCARDO … LUCIFERO</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -8395,9 +8840,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>sed084|4|no|VILARD|d28660</t>
+          <t>sed084|13|sì|LOPARDII|d28050</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8860,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8429,12 +8875,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LOPARDII</t>
+          <t>CARHONARI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lopardi Emidio</t>
+          <t>Carbonari Luigi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -8444,7 +8890,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LOMBARDI RICCARDO … LUCIFERO</t>
+          <t>CAPUA … CARIGNANI</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -8462,9 +8908,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>sed084|13|sì|LOPARDII|d28050</t>
+          <t>sed084|13|no|CARHONARI|d27500</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8943,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CARHONARI</t>
+          <t>CHIEFI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonari Luigi</t>
+          <t>Chieffi Francesco</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -8511,7 +8958,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CAPUA … CARIGNANI</t>
+          <t>CHATRIAN … CICERONE</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -8529,9 +8976,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>sed084|13|no|CARHONARI|d27500</t>
+          <t>sed084|13|no|CHIEFI|d12300</t>
         </is>
       </c>
     </row>
@@ -8563,12 +9011,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CHIEFI</t>
+          <t>COLONNA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chieffi Francesco</t>
+          <t>Colonna Di Paliano Carlo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8578,7 +9026,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CHATRIAN … CICERONE</t>
+          <t>COLITTO … CONCI ELISABETTA</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -8596,9 +9044,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>sed084|13|no|CHIEFI|d12300</t>
+          <t>sed084|13|no|COLONNA|d18390</t>
         </is>
       </c>
     </row>
@@ -8610,32 +9059,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sed084</t>
+          <t>sed086</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed084/sed084nc.pdf#page=13</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed086/sed086nc.pdf#page=17</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>COLONNA</t>
+          <t>BADINI</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Colonna Di Paliano Carlo</t>
+          <t>Badini Confalonieri Vittorio</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8645,7 +9094,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COLITTO … CONCI ELISABETTA</t>
+          <t>AZZI … BALDASSARI</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -8663,9 +9112,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>sed084|13|no|COLONNA|d18390</t>
+          <t>sed086|17|sì|BADINI|d400</t>
         </is>
       </c>
     </row>
@@ -8697,12 +9147,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BADINI</t>
+          <t>CERRETTI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Badini Confalonieri Vittorio</t>
+          <t>Cerreti Giulio</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8712,7 +9162,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AZZI … BALDASSARI</t>
+          <t>CAVALLARI … CEVOLOTTO</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -8730,9 +9180,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>sed086|17|sì|BADINI|d400</t>
+          <t>sed086|17|sì|CERRETTI|d18180</t>
         </is>
       </c>
     </row>
@@ -8764,12 +9215,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CERRETTI</t>
+          <t>CGRISPO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cerreti Giulio</t>
+          <t>Crispo Amerigo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8779,7 +9230,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CAVALLARI … CEVOLOTTO</t>
+          <t>CREMASCHI OLINDO … DAMIANI</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -8797,9 +9248,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>sed086|17|sì|CERRETTI|d18180</t>
+          <t>sed086|17|sì|CGRISPO|d27700</t>
         </is>
       </c>
     </row>
@@ -8816,7 +9268,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>congedo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -8831,22 +9283,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CGRISPO</t>
+          <t>DAMICO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crispo Amerigo</t>
+          <t>D'Amico Michele</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>omonimo risolto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CREMASCHI OLINDO … DAMIANI</t>
+          <t>CORSINI … FIORE</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -8864,9 +9316,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>sed086|17|sì|CGRISPO|d27700</t>
+          <t>sed086|17|congedo|DAMICO|d7710</t>
         </is>
       </c>
     </row>
@@ -8878,42 +9331,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>v6</t>
+          <t>v7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>congedo</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sed086</t>
+          <t>sed088</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed086/sed086nc.pdf#page=17</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed088/sed088nc.pdf#page=24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DAMICO</t>
+          <t>ARIGELUCCI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>D'Amico Michele</t>
+          <t>Angelucci Nicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>omonimo risolto</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CORSINI … FIORE</t>
+          <t>ANGELINI … ARCAINI</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -8931,9 +9384,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>sed086|17|congedo|DAMICO|d7710</t>
+          <t>sed088|24|no|ARIGELUCCI|d6460</t>
         </is>
       </c>
     </row>
@@ -8965,12 +9419,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ARIGELUCCI</t>
+          <t>BASTIAHETTO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Angelucci Nicola</t>
+          <t>Bastianetto Celeste</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8980,7 +9434,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ANGELINI … ARCAINI</t>
+          <t>BARONTINI ANELITO … BAZOLI</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -8998,9 +9452,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>sed088|24|no|ARIGELUCCI|d6460</t>
+          <t>sed088|24|no|BASTIAHETTO|d12230</t>
         </is>
       </c>
     </row>
@@ -9032,12 +9487,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BASTIAHETTO</t>
+          <t>DORIOFRIO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bastianetto Celeste</t>
+          <t>D'Onofrio Edoardo</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9047,7 +9502,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BARONTINI ANELITO … BAZOLI</t>
+          <t>DOMINEDO … DOSSETTI</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -9065,9 +9520,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>sed088|24|no|BASTIAHETTO|d12230</t>
+          <t>sed088|24|no|DORIOFRIO|d11390</t>
         </is>
       </c>
     </row>
@@ -9099,12 +9555,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DORIOFRIO</t>
+          <t>RECTA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>D'Onofrio Edoardo</t>
+          <t>Recca Raffaele</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9114,7 +9570,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DOMINEDO … DOSSETTI</t>
+          <t>RAVAGNAN … RESCIGNO</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -9132,9 +9588,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>sed088|24|no|DORIOFRIO|d11390</t>
+          <t>sed088|24|no|RECTA|d13570</t>
         </is>
       </c>
     </row>
@@ -9166,12 +9623,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RECTA</t>
+          <t>RIECIO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Recca Raffaele</t>
+          <t>Riccio Stefano</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9181,7 +9638,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>RAVAGNAN … RESCIGNO</t>
+          <t>RICCI GIUSEPPE … RIVERA</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -9199,9 +9656,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>sed088|24|no|RECTA|d13570</t>
+          <t>sed088|24|no|RIECIO|d5030</t>
         </is>
       </c>
     </row>
@@ -9213,42 +9671,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>v7</t>
+          <t>v8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sed088</t>
+          <t>sed102</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed088/sed088nc.pdf#page=24</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=16</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RIECIO</t>
+          <t>MORELLI</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Riccio Stefano</t>
+          <t>Morelli Renato</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>omonimo risolto</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>RICCI GIUSEPPE … RIVERA</t>
+          <t>MONTEMARTINI … MORINI</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -9266,9 +9724,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>sed088|24|no|RIECIO|d5030</t>
+          <t>sed102|16|sì|MORELLI|d9440</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9744,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -9300,22 +9759,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MORELLI</t>
+          <t>AMALEI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Morelli Renato</t>
+          <t>Amadei Leonetto</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>omonimo risolto</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MONTEMARTINI … MORINI</t>
+          <t>ALLEGATO … AMBROSINI</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -9333,9 +9792,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>sed102|16|sì|MORELLI|d9440</t>
+          <t>sed102|16|no|AMALEI|d6370</t>
         </is>
       </c>
     </row>
@@ -9367,12 +9827,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AMALEI</t>
+          <t>DEMINEDO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Amadei Leonetto</t>
+          <t>Dominedo' Francesco Maria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -9382,7 +9842,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ALLEGATO … AMBROSINI</t>
+          <t>DI VITTORIO … DONOFRIO</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -9400,9 +9860,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>sed102|16|no|AMALEI|d6370</t>
+          <t>sed102|16|no|DEMINEDO|d25760</t>
         </is>
       </c>
     </row>
@@ -9434,12 +9895,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DEMINEDO</t>
+          <t>NOTARIARINI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dominedo' Francesco Maria</t>
+          <t>Notarianni Giuseppe</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -9449,7 +9910,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DI VITTORIO … DONOFRIO</t>
+          <t>NOBILI ORO … NOVELLA</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -9467,9 +9928,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>sed102|16|no|DEMINEDO|d25760</t>
+          <t>sed102|16|no|NOTARIARINI|d12280</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9963,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NOTARIARINI</t>
+          <t>TESTITORI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Notarianni Giuseppe</t>
+          <t>Tessitori Tiziano</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -9516,7 +9978,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NOBILI ORO … NOVELLA</t>
+          <t>TERRANOVA … TOGLIATTI</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -9534,9 +9996,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>sed102|16|no|NOTARIARINI|d12280</t>
+          <t>sed102|16|no|TESTITORI|d28560</t>
         </is>
       </c>
     </row>
@@ -9548,12 +10011,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>v8</t>
+          <t>v9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -9563,27 +10026,27 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=16</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=54</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAVIA</t>
+          <t>MASTINO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Taviani Paolo Emilio</t>
+          <t>Mastino Gesumino</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>omonimo risolto</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TARGETTI … TEGA</t>
+          <t>MARZAROTTO … MASTROJANNI</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -9601,9 +10064,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>sed102|16|no|TAVIA|d200929</t>
+          <t>sed102|54|sì|MASTINO|d26390</t>
         </is>
       </c>
     </row>
@@ -9615,12 +10079,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>v8</t>
+          <t>v9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -9630,17 +10094,17 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=16</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=54</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TESTITORI</t>
+          <t>PALLASTRELI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tessitori Tiziano</t>
+          <t>Pallastrelli Giovanni</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -9650,7 +10114,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TERRANOVA … TOMBA</t>
+          <t>ORLANDO CAMILLO … PASTORE GIULIO</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -9668,9 +10132,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>sed102|16|no|TESTITORI|d28560</t>
+          <t>sed102|54|sì|PALLASTRELI|d28280</t>
         </is>
       </c>
     </row>
@@ -9682,7 +10147,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>v9</t>
+          <t>v10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9692,32 +10157,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sed102</t>
+          <t>sed104</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=54</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=21</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MASTINO</t>
+          <t>GIOHTTI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mastino Gesumino</t>
+          <t>Giolitti Antonio</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>omonimo risolto</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MARZAROTTO … MASTROJANNI</t>
+          <t>GHIDINI … GIUA</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -9735,9 +10200,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>sed102|54|sì|MASTINO|d26390</t>
+          <t>sed104|21|sì|GIOHTTI|d2930</t>
         </is>
       </c>
     </row>
@@ -9749,7 +10215,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>v9</t>
+          <t>v10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9759,22 +10225,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>sed102</t>
+          <t>sed104</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=54</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PALLASTRELI</t>
+          <t>SIMONRINI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pallastrelli Giovanni</t>
+          <t>Simonini Alberto</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -9784,7 +10250,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ORLANDO CAMILLO … PASTORE GIULIO</t>
+          <t>SILIPO … SPALLIECI</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -9802,9 +10268,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>sed102|54|sì|PALLASTRELI|d28280</t>
+          <t>sed104|21|sì|SIMONRINI|d12330</t>
         </is>
       </c>
     </row>
@@ -9836,22 +10303,22 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GIOHTTI</t>
+          <t>SPALLIECI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Giolitti Antonio</t>
+          <t>Spallicci Aldo</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>GHIDINI … GIUA</t>
+          <t>SIMONRINI … STAMPACCHIA</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -9869,9 +10336,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>sed104|21|sì|GIOHTTI|d2930</t>
+          <t>sed104|21|sì|SPALLIECI|d28520</t>
         </is>
       </c>
     </row>
@@ -9888,7 +10356,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9903,12 +10371,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SIMONRINI</t>
+          <t>CATELLESSA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Simonini Alberto</t>
+          <t>Cotellessa Mario</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -9918,7 +10386,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SILIPO … SPALLIECI</t>
+          <t>CORSANEGO … COVELLI</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -9936,9 +10404,14 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lettura dell'immagine: «Co-/tellessa» fra Corsanego e Covelli</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>sed104|21|sì|SIMONRINI|d12330</t>
+          <t>sed104|21|no|CATELLESSA|d7610</t>
         </is>
       </c>
     </row>
@@ -9955,7 +10428,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9970,12 +10443,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SPALLIECI</t>
+          <t>TAMBRONI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Spallicci Aldo</t>
+          <t>Tambroni Armaroli Ferdinando</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -9985,7 +10458,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SIMONRINI … STAMPACCHIA</t>
+          <t>SULLO FIORENTINO … TAVIANI</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -10003,9 +10476,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>sed104|21|sì|SPALLIECI|d28520</t>
+          <t>sed104|21|no|TAMBRONI|d12540</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10496,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>congedo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -10037,22 +10511,22 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FEDE</t>
+          <t>CANEYARI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Federici Maria</t>
+          <t>Canevari Emilio</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FANTONI … FERRARESE</t>
+          <t>CAIRO … CAPRANI</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -10070,9 +10544,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>sed104|21|no|FEDE|d8120</t>
+          <t>sed104|21|congedo|CANEYARI|d27450</t>
         </is>
       </c>
     </row>
@@ -10084,12 +10559,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>v10</t>
+          <t>v11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -10099,17 +10574,17 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=21</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=26</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TAMBRONI</t>
+          <t>BAECICONI</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tambroni Armaroli Ferdinando</t>
+          <t>Bacciconi Luigi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -10119,7 +10594,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SULLO FIORENTINO … TAVIANI</t>
+          <t>AVANZINI … BALDUZZI</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -10137,9 +10612,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>sed104|21|no|TAMBRONI|d12540</t>
+          <t>sed104|26|sì|BAECICONI|d6520</t>
         </is>
       </c>
     </row>
@@ -10151,12 +10627,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>v10</t>
+          <t>v11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>congedo</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -10166,17 +10642,17 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=21</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=26</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CANEYARI</t>
+          <t>MUURDACA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Canevari Emilio</t>
+          <t>Murdaca Filippo</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -10186,7 +10662,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CAIRO … CAPRANI</t>
+          <t>MOTOLESE … MURGIA</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -10204,9 +10680,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>sed104|21|congedo|CANEYARI|d27450</t>
+          <t>sed104|26|sì|MUURDACA|d19380</t>
         </is>
       </c>
     </row>
@@ -10238,12 +10715,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BAECICONI</t>
+          <t>RESTA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bacciconi Luigi</t>
+          <t>Restagno Pier Carlo</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -10253,7 +10730,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AVANZINI … BALDUZZI</t>
+          <t>RESCIGNO … RICCIO STEFANO</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -10271,9 +10748,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>sed104|26|sì|BAECICONI|d6520</t>
+          <t>sed104|26|sì|RESTA|d28410</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10763,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>v11</t>
+          <t>v12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10295,22 +10773,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>sed104</t>
+          <t>sed105</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=26</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed105/sed105nc.pdf#page=15</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MUURDACA</t>
+          <t>BERNAMONFI</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Murdaca Filippo</t>
+          <t>Bernamonti Dante</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -10320,7 +10798,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>MOTOLESE … MURGIA</t>
+          <t>BERNABEI … BERNINI FERDINANDO</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -10338,9 +10816,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>sed104|26|sì|MUURDACA|d19380</t>
+          <t>sed105|15|sì|BERNAMONFI|d11490</t>
         </is>
       </c>
     </row>
@@ -10352,32 +10831,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>v11</t>
+          <t>v13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>sed104</t>
+          <t>sed129</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=26</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed129/sed129nc.pdf#page=35</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RESTA</t>
+          <t>BETTIO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Restagno Pier Carlo</t>
+          <t>Bettiol Giuseppe Maria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -10387,7 +10866,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>RESCIGNO … RICCIO STEFANO</t>
+          <t>BERTONE … BIAGIONI</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -10405,9 +10884,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>sed104|26|sì|RESTA|d28410</t>
+          <t>sed129|35|no|BETTIO|d17950</t>
         </is>
       </c>
     </row>
@@ -10419,32 +10899,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>v12</t>
+          <t>v13</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>sed105</t>
+          <t>sed129</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed105/sed105nc.pdf#page=15</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed129/sed129nc.pdf#page=35</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BERNAMONFI</t>
+          <t>CGAIATI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bernamonti Dante</t>
+          <t>Caiati Italo Giulio</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10454,7 +10934,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>BERNABEI … BERNINI FERDINANDO</t>
+          <t>CACCURI … CALDERA</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -10472,9 +10952,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>sed105|15|sì|BERNAMONFI|d11490</t>
+          <t>sed129|35|no|CGAIATI|d1250</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10987,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BETTIO</t>
+          <t>PALMA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bettiol Giuseppe Maria</t>
+          <t>De Palma Giacomo</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10521,7 +11002,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>BERTONE … BIAGIONI</t>
+          <t>DE MICHELIS PAOLO … JERVOLINO MARIA MARIA</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -10539,9 +11020,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>sed129|35|no|BETTIO|d17950</t>
+          <t>sed129|35|no|PALMA|d17200</t>
         </is>
       </c>
     </row>
@@ -10553,32 +11035,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>v13</t>
+          <t>v14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>sed129</t>
+          <t>sed177</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed129/sed129nc.pdf#page=35</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed177/sed177nc.pdf#page=17</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CGAIATI</t>
+          <t>ORENTINO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Caiati Italo Giulio</t>
+          <t>Fiorentino Giosue'</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10588,7 +11070,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CACCURI … CALDERA</t>
+          <t>FIORE … FOGAGNOLO</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -10606,9 +11088,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>sed129|35|no|CGAIATI|d1250</t>
+          <t>sed177|17|sì|ORENTINO|d8180</t>
         </is>
       </c>
     </row>
@@ -10620,7 +11103,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>v13</t>
+          <t>v15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10630,22 +11113,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>sed129</t>
+          <t>sed178</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed129/sed129nc.pdf#page=35</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed178/sed178nc.pdf#page=16</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PALMA</t>
+          <t>CHIEFII</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>De Palma Giacomo</t>
+          <t>Chieffi Francesco</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -10655,7 +11138,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DE MICHELIS PAOLO … JERVOLINO MARIA MARIA</t>
+          <t>CHATRIAN … CHIOSTERGI</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -10673,9 +11156,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>sed129|35|no|PALMA|d17200</t>
+          <t>sed178|16|no|CHIEFII|d12300</t>
         </is>
       </c>
     </row>
@@ -10687,7 +11171,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>v14</t>
+          <t>v16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -10697,22 +11181,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sed177</t>
+          <t>sed180</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed177/sed177nc.pdf#page=17</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=13</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ORENTINO</t>
+          <t>BASLIANETTO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fiorentino Giosue'</t>
+          <t>Bastianetto Celeste</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -10722,7 +11206,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FIORE … FOGAGNOLO</t>
+          <t>BALDUZZI … BELLATO</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -10740,9 +11224,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>sed177|17|sì|ORENTINO|d8180</t>
+          <t>sed180|13|sì|BASLIANETTO|d12230</t>
         </is>
       </c>
     </row>
@@ -10754,32 +11239,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>v15</t>
+          <t>v16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>sed178</t>
+          <t>sed180</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed178/sed178nc.pdf#page=16</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=13</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CHIEFII</t>
+          <t>GOTELL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chieffi Francesco</t>
+          <t>Gotelli Angela</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -10789,7 +11274,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CHATRIAN … CHIOSTERGI</t>
+          <t>GONELLA … GRASSI</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -10807,9 +11292,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>sed178|16|no|CHIEFII|d12300</t>
+          <t>sed180|13|sì|GOTELL|d8610</t>
         </is>
       </c>
     </row>
@@ -10826,7 +11312,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -10841,22 +11327,22 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BASLIANETTO</t>
+          <t>GAUSI</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bastianetto Celeste</t>
+          <t>Li Causi Girolamo</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>BALDUZZI … BELLATO</t>
+          <t>LA ROCCA … LOMBARDI CARLO</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -10874,9 +11360,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>sed180|13|sì|BASLIANETTO|d12230</t>
+          <t>sed180|13|no|GAUSI|d26200</t>
         </is>
       </c>
     </row>
@@ -10893,7 +11380,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -10908,12 +11395,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GOTELL</t>
+          <t>VONI</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gotelli Angela</t>
+          <t>Veroni Dante</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -10923,7 +11410,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>GONELLA … GRASSI</t>
+          <t>VERNOCCHI … VIGNA</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -10941,9 +11428,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>sed180|13|sì|GOTELL|d8610</t>
+          <t>sed180|13|no|VONI|d28650</t>
         </is>
       </c>
     </row>
@@ -10955,12 +11443,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>v16</t>
+          <t>v17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10970,27 +11458,27 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=13</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=16</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GAUSI</t>
+          <t>BOVELTI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Li Causi Girolamo</t>
+          <t>Bovetti Giovanni</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>LA ROCCA … LOMBARDI CARLO</t>
+          <t>BOSCO LUCARELLI … BRASCHI</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -11008,9 +11496,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>sed180|13|no|GAUSI|d26200</t>
+          <t>sed180|16|sì|BOVELTI|d12350</t>
         </is>
       </c>
     </row>
@@ -11022,12 +11511,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>v16</t>
+          <t>v17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -11037,17 +11526,17 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=13</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=16</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VONI</t>
+          <t>CARIISTIA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Veroni Dante</t>
+          <t>Caristia Carmelo</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -11057,7 +11546,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>VERNOCCHI … VIGNA</t>
+          <t>CARBONI ENRICO … CAROLEO</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -11075,9 +11564,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>sed180|13|no|VONI|d28650</t>
+          <t>sed180|16|sì|CARIISTIA|d27530</t>
         </is>
       </c>
     </row>
@@ -11109,12 +11599,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BOVELTI</t>
+          <t>SCEHIRAITI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bovetti Giovanni</t>
+          <t>Schiratti Guglielmo</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -11124,7 +11614,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BOSCO LUCARELLI … BRASCHI</t>
+          <t>SCELBA … SCOTTI ALESSANDRO</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -11142,9 +11632,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>sed180|16|sì|BOVELTI|d12350</t>
+          <t>sed180|16|sì|SCEHIRAITI|d13040</t>
         </is>
       </c>
     </row>
@@ -11176,12 +11667,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CARIISTIA</t>
+          <t>ZVUCCARINI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Caristia Carmelo</t>
+          <t>Zuccarini Oliviero</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -11191,7 +11682,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CARBONI ENRICO … CAROLEO</t>
+          <t xml:space="preserve">ZOTTA … </t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -11209,9 +11700,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>sed180|16|sì|CARIISTIA|d27530</t>
+          <t>sed180|16|sì|ZVUCCARINI|d27120</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11720,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -11243,12 +11735,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SCEHIRAITI</t>
+          <t>PISTUIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Schiratti Guglielmo</t>
+          <t>Pistoia Umberto</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -11258,7 +11750,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SCELBA … SCOTTI ALESSANDRO</t>
+          <t>PESENTI … PLATONE</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -11276,9 +11768,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>sed180|16|sì|SCEHIRAITI|d13040</t>
+          <t>sed180|16|no|PISTUIA|d26710</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11788,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -11310,12 +11803,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ZVUCCARINI</t>
+          <t>PRATOLONGA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zuccarini Oliviero</t>
+          <t>Pratolongo Giordano</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -11325,7 +11818,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOTTA … </t>
+          <t>POLLASTRINI ELETTRA … PRESSINOTTI</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -11343,9 +11836,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>sed180|16|sì|ZVUCCARINI|d27120</t>
+          <t>sed180|16|no|PRATOLONGA|d13840</t>
         </is>
       </c>
     </row>
@@ -11357,32 +11851,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>v17</t>
+          <t>v18</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>sed180</t>
+          <t>sed187</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=16</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed187/sed187nc.pdf#page=16</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PISTUIA</t>
+          <t>UALLICO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pistoia Umberto</t>
+          <t>Gallico Nadia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -11392,7 +11886,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>PESENTI … PLATONE</t>
+          <t>FORNARA … GASPAROTTO</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -11410,9 +11904,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>sed180|16|no|PISTUIA|d26710</t>
+          <t>sed187|16|sì|UALLICO|d8380</t>
         </is>
       </c>
     </row>
@@ -11424,42 +11919,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>v17</t>
+          <t>v18</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>sed180</t>
+          <t>sed187</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed180/sed180nc.pdf#page=16</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed187/sed187nc.pdf#page=16</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PRATOLONGA</t>
+          <t>GIOHTTI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pratolongo Giordano</t>
+          <t>Giolitti Antonio</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>POLLASTRINI ELETTRA … PRESSINOTTI</t>
+          <t>GHISLANDI … GIUA</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -11477,9 +11972,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>sed180|16|no|PRATOLONGA|d13840</t>
+          <t>sed187|16|sì|GIOHTTI|d2930</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11992,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11511,12 +12007,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UALLICO</t>
+          <t>COLONNETT</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gallico Nadia</t>
+          <t>Colonnetti Gustavo</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -11526,7 +12022,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>FORNARA … GASPAROTTO</t>
+          <t>COLITTO … CONCI ELISABETTA</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -11544,9 +12040,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>sed187|16|sì|UALLICO|d8380</t>
+          <t>sed187|16|no|COLONNETT|d11360</t>
         </is>
       </c>
     </row>
@@ -11563,7 +12060,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11578,12 +12075,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GIOHTTI</t>
+          <t>CURTE</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Giolitti Antonio</t>
+          <t>Del Curto Giovanni</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -11593,7 +12090,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>GHISLANDI … GIUA</t>
+          <t>DE FALCO … DELLI CASTELLI FILOMENA</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -11611,9 +12108,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>sed187|16|sì|GIOHTTI|d2930</t>
+          <t>sed187|16|no|CURTE|d27750</t>
         </is>
       </c>
     </row>
@@ -11645,22 +12143,22 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>COLONNETT</t>
+          <t>EINAUVA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Colonnetti Gustavo</t>
+          <t>Einaudi Luigi</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COLITTO … CONCI ELISABETTA</t>
+          <t>DOSSETTI … FABBRI</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -11678,9 +12176,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>sed187|16|no|COLONNETT|d11360</t>
+          <t>sed187|16|no|EINAUVA|d27790</t>
         </is>
       </c>
     </row>
@@ -11712,22 +12211,22 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CURTE</t>
+          <t>FROGGIA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Del Curto Giovanni</t>
+          <t>Froggio Giacinto</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>DE FALCO … DELLI CASTELLI FILOMENA</t>
+          <t>FRANCESCHINI … GABRIELI</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -11745,9 +12244,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>sed187|16|no|CURTE|d27750</t>
+          <t>sed187|16|no|FROGGIA|d18780</t>
         </is>
       </c>
     </row>
@@ -11759,32 +12259,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>v18</t>
+          <t>v19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>sed187</t>
+          <t>sed188</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed187/sed187nc.pdf#page=16</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed188/sed188nc.pdf#page=15</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>EINAUVA</t>
+          <t>GAUSI</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Einaudi Luigi</t>
+          <t>Li Causi Girolamo</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11794,7 +12294,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>DOSSETTI … FABBRI</t>
+          <t>LEONE FRANCESCO … LIZZADRI</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -11812,9 +12312,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>sed187|16|no|EINAUVA|d27790</t>
+          <t>sed188|15|sì|GAUSI|d26200</t>
         </is>
       </c>
     </row>
@@ -11826,42 +12327,42 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>v18</t>
+          <t>v19</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>sed187</t>
+          <t>sed188</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed187/sed187nc.pdf#page=16</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed188/sed188nc.pdf#page=15</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FROGGIA</t>
+          <t>MONTALFO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Froggio Giacinto</t>
+          <t>Montalbano Giuseppe</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>FRANCESCHINI … GABRIELI</t>
+          <t>MONTAGNANA RITA … MORANDI</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -11879,9 +12380,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>sed187|16|no|FROGGIA|d18780</t>
+          <t>sed188|15|sì|MONTALFO|d9390</t>
         </is>
       </c>
     </row>
@@ -11913,12 +12415,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GAUSI</t>
+          <t>PRELL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Li Causi Girolamo</t>
+          <t>Preti Luigi</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11928,7 +12430,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LEONE FRANCESCO … LIZZADRI</t>
+          <t>PRESSINOTTI … PREZIOSI</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -11946,9 +12448,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>sed188|15|sì|GAUSI|d26200</t>
+          <t>sed188|15|sì|PRELL|d4810</t>
         </is>
       </c>
     </row>
@@ -11980,22 +12483,22 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MONTALFO</t>
+          <t>ROSSI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Montalbano Giuseppe</t>
+          <t>Rossi Maria Maddalena</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>omonimo risolto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MONTAGNANA RITA … MORANDI</t>
+          <t>ROSSI GIUSEPPE … ROSSI PAOLO</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -12013,9 +12516,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>sed188|15|sì|MONTALFO|d9390</t>
+          <t>sed188|15|sì|ROSSI|d10090</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12536,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12047,22 +12551,22 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PRELL</t>
+          <t>CONCL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Preti Luigi</t>
+          <t>Conci Elisabetta</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>PRESSINOTTI … PREZIOSI</t>
+          <t>COLONNETTI … CONTI</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -12080,9 +12584,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>sed188|15|sì|PRELL|d4810</t>
+          <t>sed188|15|no|CONCL|d25630</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12604,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12114,22 +12619,22 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ROSSI</t>
+          <t>VANOM</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rossi Maria Maddalena</t>
+          <t>Vanoni Ezio</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>omonimo risolto</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ROSSI GIUSEPPE … ROSSI PAOLO</t>
+          <t>VALMARANA … VIALE</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -12147,9 +12652,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>sed188|15|sì|ROSSI|d10090</t>
+          <t>sed188|15|no|VANOM|d28640</t>
         </is>
       </c>
     </row>
@@ -12161,7 +12667,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>v19</t>
+          <t>v20</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -12171,22 +12677,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>sed188</t>
+          <t>sed229</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed188/sed188nc.pdf#page=15</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed229/sed229nc.pdf#page=8</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CONCL</t>
+          <t>AYROLDI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Conci Elisabetta</t>
+          <t>Ayroldi Carissimo Giuseppe</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12196,7 +12702,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COLONNETTI … CONTI</t>
+          <t>ASSENNATO … AZZI</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -12214,9 +12720,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>sed188|15|no|CONCL|d25630</t>
+          <t>sed229|8|no|AYROLDI|d27160</t>
         </is>
       </c>
     </row>
@@ -12228,7 +12735,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>v19</t>
+          <t>v20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12238,32 +12745,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>sed188</t>
+          <t>sed229</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed188/sed188nc.pdf#page=15</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed229/sed229nc.pdf#page=8</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VANOM</t>
+          <t>DONOFRO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Vanoni Ezio</t>
+          <t>D'Onofrio Edoardo</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>VALMARANA … VIALE</t>
+          <t>DONATI … DOZZA</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -12281,9 +12788,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>sed188|15|no|VANOM|d28640</t>
+          <t>sed229|8|no|DONOFRO|d11390</t>
         </is>
       </c>
     </row>
@@ -12315,22 +12823,22 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AYROLDI</t>
+          <t>LACOTII</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ayroldi Carissimo Giuseppe</t>
+          <t>Laconi Renzo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ASSENNATO … AZZI</t>
+          <t>LABRIOLA … LAGRAVINESE PASQUALE</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -12348,9 +12856,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>sed229|8|no|AYROLDI|d27160</t>
+          <t>sed229|8|no|LACOTII|d11820</t>
         </is>
       </c>
     </row>
@@ -12362,32 +12871,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>v20</t>
+          <t>v21</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>sed229</t>
+          <t>sed260</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed229/sed229nc.pdf#page=8</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed260/sed260nc.pdf#page=13</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DONOFRO</t>
+          <t>LUEIFERO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>D'Onofrio Edoardo</t>
+          <t>Lucifero Roberto</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12397,7 +12906,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DONATI … DOZZA</t>
+          <t>LOMBARDO IVAN MATTEO … LUISETTI</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -12415,9 +12924,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>sed229|8|no|DONOFRO|d11390</t>
+          <t>sed260|13|sì|LUEIFERO|d8950</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12939,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>v20</t>
+          <t>v21</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12439,32 +12949,32 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>sed229</t>
+          <t>sed260</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed229/sed229nc.pdf#page=8</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed260/sed260nc.pdf#page=13</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LACOTII</t>
+          <t>BASTIANETFO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Laconi Renzo</t>
+          <t>Bastianetto Celeste</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>LABRIOLA … LAGRAVINESE PASQUALE</t>
+          <t>BARACCO … BELLUSCI</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -12482,9 +12992,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>sed229|8|no|LACOTII|d11820</t>
+          <t>sed260|13|no|BASTIANETFO|d12230</t>
         </is>
       </c>
     </row>
@@ -12501,7 +13012,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12516,12 +13027,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LUEIFERO</t>
+          <t>STARNUTI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lucifero Roberto</t>
+          <t>Lami Starnuti Edgardo</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12531,7 +13042,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LOMBARDO IVAN MATTEO … LUISETTI</t>
+          <t>JERVOLINO … LA PIRA</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -12549,9 +13060,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>sed260|13|sì|LUEIFERO|d8950</t>
+          <t>sed260|13|no|STARNUTI|d18990</t>
         </is>
       </c>
     </row>
@@ -12583,12 +13095,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BASTIANETFO</t>
+          <t>MASTROJANRI</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bastianetto Celeste</t>
+          <t>Mastrojanni Ottavio</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12598,7 +13110,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>BARACCO … BELLUSCI</t>
+          <t>MARTINELLI … MATTARELLA</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
@@ -12616,9 +13128,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>sed260|13|no|BASTIANETFO|d12230</t>
+          <t>sed260|13|no|MASTROJANRI|d26400</t>
         </is>
       </c>
     </row>
@@ -12650,12 +13163,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>STARNUTI</t>
+          <t>REGNONI</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lami Starnuti Edgardo</t>
+          <t>Rognoni Arturo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12665,7 +13178,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>JERVOLINO … LA PIRA</t>
+          <t>RODINO UGO … ROMANO</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -12683,9 +13196,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>sed260|13|no|STARNUTI|d18990</t>
+          <t>sed260|13|no|REGNONI|d10060</t>
         </is>
       </c>
     </row>
@@ -12717,12 +13231,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MASTROJANRI</t>
+          <t>SIMENINI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Mastrojanni Ottavio</t>
+          <t>Simonini Alberto</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12732,7 +13246,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MARTINELLI … MATTARELLA</t>
+          <t>SEGNI … SPALLICCI</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -12750,9 +13264,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>sed260|13|no|MASTROJANRI|d26400</t>
+          <t>sed260|13|no|SIMENINI|d12330</t>
         </is>
       </c>
     </row>
@@ -12784,12 +13299,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>REGNONI</t>
+          <t>TITOMANLIE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rognoni Arturo</t>
+          <t>Titomanlio Vittoria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12799,7 +13314,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>RODINO UGO … ROMANO</t>
+          <t>TESSITORI … TOGNI</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -12817,9 +13332,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>sed260|13|no|REGNONI|d10060</t>
+          <t>sed260|13|no|TITOMANLIE|d10600</t>
         </is>
       </c>
     </row>
@@ -12851,12 +13367,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SIMENINI</t>
+          <t>VERENI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Simonini Alberto</t>
+          <t>Veroni Dante</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -12866,7 +13382,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SEGNI … SPALLICCI</t>
+          <t>VANONI … VIALE</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -12884,9 +13400,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>sed260|13|no|SIMENINI|d12330</t>
+          <t>sed260|13|no|VERENI|d28650</t>
         </is>
       </c>
     </row>
@@ -12898,32 +13415,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>v21</t>
+          <t>v22</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>sed260</t>
+          <t>sed269</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed260/sed260nc.pdf#page=13</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed269/sed269nc.pdf#page=18</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TITOMANLIE</t>
+          <t>CONCII</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Titomanlio Vittoria</t>
+          <t>Conci Elisabetta</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -12933,7 +13450,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>TESSITORI … TOGNI</t>
+          <t>COLOMBO EMILIO … CONDORELLI</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -12951,9 +13468,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>sed260|13|no|TITOMANLIE|d10600</t>
+          <t>sed269|18|sì|CONCII|d25630</t>
         </is>
       </c>
     </row>
@@ -12965,32 +13483,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>v21</t>
+          <t>v22</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>sed260</t>
+          <t>sed269</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed260/sed260nc.pdf#page=13</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed269/sed269nc.pdf#page=18</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VERENI</t>
+          <t>TESSITERI</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Veroni Dante</t>
+          <t>Tessitori Tiziano</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13000,7 +13518,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>VANONI … VIALE</t>
+          <t>TAVIANI … TITOMANLIO VITTORIA</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -13018,9 +13536,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>sed260|13|no|VERENI|d28650</t>
+          <t>sed269|18|sì|TESSITERI|d28560</t>
         </is>
       </c>
     </row>
@@ -13052,12 +13571,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CONCII</t>
+          <t>TOSA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Conci Elisabetta</t>
+          <t>Tosato Egidio</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13067,7 +13586,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>COLOMBO EMILIO … CONDORELLI</t>
+          <t>TOGNI … TOSI</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -13085,9 +13604,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>sed269|18|sì|CONCII|d25630</t>
+          <t>sed269|18|sì|TOSA|d10630</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13619,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>v22</t>
+          <t>v23</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -13109,22 +13629,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>sed269</t>
+          <t>sed270</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed269/sed269nc.pdf#page=18</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed270/sed270nc.pdf#page=18</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>TESSITERI</t>
+          <t>BERNE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tessitori Tiziano</t>
+          <t>Bertone Giovanni Battista</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13134,7 +13654,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>TAVIANI … TITOMANLIO VITTORIA</t>
+          <t>BEI ADELE … BIANCHI BRUNO</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -13149,12 +13669,13 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>giusto</t>
-        </is>
-      </c>
+          <t>Bernamonti Dante</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>sed269|18|sì|TESSITERI|d28560</t>
+          <t>sed270|18|sì|BERNE|d27320</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13687,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>v22</t>
+          <t>v24</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -13176,32 +13697,32 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>sed269</t>
+          <t>sed277</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed269/sed269nc.pdf#page=18</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed277/sed277nc.pdf#page=7</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>TOSA</t>
+          <t>BIFINI</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tosato Egidio</t>
+          <t>Binni Walter</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TOGNI … TOSI</t>
+          <t>BIANCHI BRUNO … BITOSSI</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -13219,9 +13740,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>sed269|18|sì|TOSA|d10630</t>
+          <t>sed277|7|sì|BIFINI|d6970</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13755,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>v23</t>
+          <t>v24</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -13243,22 +13765,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>sed270</t>
+          <t>sed277</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed270/sed270nc.pdf#page=18</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed277/sed277nc.pdf#page=7</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BERNE</t>
+          <t>RUSGGERI</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bertone Giovanni Battista</t>
+          <t>Ruggeri Luigi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -13268,7 +13790,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>BEI ADELE … BIANCHI BRUNO</t>
+          <t>ROSSI MARIA MADDALENA … RUGGIERO CARLO</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -13283,12 +13805,13 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>Bernamonti Dante</t>
-        </is>
-      </c>
+          <t>giusto</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>sed270|18|sì|BERNE|d27320</t>
+          <t>sed277|7|sì|RUSGGERI|d19820</t>
         </is>
       </c>
     </row>
@@ -13320,22 +13843,22 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BIFINI</t>
+          <t>SARISONE</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Binni Walter</t>
+          <t>Sansone Luigi Renato</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>BIANCHI BRUNO … BITOSSI</t>
+          <t>SALERNO … SANTI</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -13353,9 +13876,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>sed277|7|sì|BIFINI|d6970</t>
+          <t>sed277|7|sì|SARISONE|d26890</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13896,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13387,12 +13911,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RUSGGERI</t>
+          <t>BENVERUTI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ruggeri Luigi</t>
+          <t>Benvenuti Lodovico Sforza</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -13402,7 +13926,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ROSSI MARIA MADDALENA … RUGGIERO CARLO</t>
+          <t>BENEDETTINI … BERGAMINI</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -13420,9 +13944,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>sed277|7|sì|RUSGGERI|d19820</t>
+          <t>sed277|7|no|BENVERUTI|d11330</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13964,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13454,12 +13979,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SARISONE</t>
+          <t>MALVESFITI</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sansone Luigi Renato</t>
+          <t>Malvestiti Piero</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -13469,7 +13994,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SALERNO … SANTI</t>
+          <t>LIZIER … MANNIRONI</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -13487,9 +14012,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>sed277|7|sì|SARISONE|d26890</t>
+          <t>sed277|7|no|MALVESFITI|d12490</t>
         </is>
       </c>
     </row>
@@ -13521,12 +14047,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BENVERUTI</t>
+          <t>PERRONE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Benvenuti Lodovico Sforza</t>
+          <t>Perrone Capano Giuseppe</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -13536,7 +14062,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>BENEDETTINI … BERGAMINI</t>
+          <t>PERLINGIERI … PERUGI</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -13554,9 +14080,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>sed277|7|no|BENVERUTI|d11330</t>
+          <t>sed277|7|no|PERRONE|d9780</t>
         </is>
       </c>
     </row>
@@ -13568,7 +14095,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>v24</t>
+          <t>v25</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -13578,22 +14105,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>sed277</t>
+          <t>sed296</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed277/sed277nc.pdf#page=7</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed296/sed296nc.pdf#page=27</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MALVESFITI</t>
+          <t>CHEFFI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Malvestiti Piero</t>
+          <t>Chieffi Francesco</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -13603,7 +14130,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>LIZIER … MANNIRONI</t>
+          <t>CHIARINI … CHIOSTERGI</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -13621,9 +14148,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>sed277|7|no|MALVESFITI|d12490</t>
+          <t>sed296|27|no|CHEFFI|d12300</t>
         </is>
       </c>
     </row>
@@ -13635,7 +14163,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>v24</t>
+          <t>v25</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -13645,22 +14173,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>sed277</t>
+          <t>sed296</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed277/sed277nc.pdf#page=7</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed296/sed296nc.pdf#page=27</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PERRONE</t>
+          <t>FILLPPINI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Perrone Capano Giuseppe</t>
+          <t>Filippini Giuseppe</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -13670,7 +14198,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>PERLINGIERI … PERUGI</t>
+          <t>FERRARIO CELESTINO … FIORE</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -13688,9 +14216,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>sed277|7|no|PERRONE|d9780</t>
+          <t>sed296|27|no|FILLPPINI|d27870</t>
         </is>
       </c>
     </row>
@@ -13722,12 +14251,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CHEFFI</t>
+          <t>FJACOMETTI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chieffi Francesco</t>
+          <t>Jacometti Alberto</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -13737,7 +14266,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>CHIARINI … CHIOSTERGI</t>
+          <t>IOTTI NILDE … LACONI</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -13755,9 +14284,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>sed296|27|no|CHEFFI|d12300</t>
+          <t>sed296|27|no|FJACOMETTI|d8770</t>
         </is>
       </c>
     </row>
@@ -13789,12 +14319,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FILLPPINI</t>
+          <t>MARIGHI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Filippini Giuseppe</t>
+          <t>Merighi Mario</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -13804,7 +14334,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>FERRARIO CELESTINO … FIORE</t>
+          <t>MEDA LUIGI … MERLIN ANGELINA</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
@@ -13822,9 +14352,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>sed296|27|no|FILLPPINI|d27870</t>
+          <t>sed296|27|no|MARIGHI|d11880</t>
         </is>
       </c>
     </row>
@@ -13856,22 +14387,22 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FJACOMETTI</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Jacometti Alberto</t>
+          <t>Mole' Enrico</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>IOTTI NILDE … LACONI</t>
+          <t>MINIO … MOLINELLI</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -13889,9 +14420,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>sed296|27|no|FJACOMETTI|d8770</t>
+          <t>sed296|27|no|MALE|d28180</t>
         </is>
       </c>
     </row>
@@ -13923,22 +14455,22 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MARIGHI</t>
+          <t>MONTAG</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Merighi Mario</t>
+          <t>Montalbano Giuseppe</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>MEDA LUIGI … MERLIN ANGELINA</t>
+          <t>MOMIGLIANO … MONTINI</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -13953,12 +14485,13 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>giusto</t>
-        </is>
-      </c>
+          <t>Montagnana Mario</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>sed296|27|no|MARIGHI|d11880</t>
+          <t>sed296|27|no|MONTAG|d9390</t>
         </is>
       </c>
     </row>
@@ -13990,12 +14523,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>SUIPO</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Mole' Enrico</t>
+          <t>Silipo Luigi</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -14005,7 +14538,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>MINIO … MOLINELLI</t>
+          <t>SICIGNANO … SPALLICCI</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -14023,9 +14556,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>sed296|27|no|MALE|d28180</t>
+          <t>sed296|27|no|SUIPO|d10410</t>
         </is>
       </c>
     </row>
@@ -14037,42 +14571,42 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>v25</t>
+          <t>v26</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>sed296</t>
+          <t>sed301</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed296/sed296nc.pdf#page=27</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed301/sed301nc.pdf#page=7</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MONTAG</t>
+          <t>BINNII</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Montalbano Giuseppe</t>
+          <t>Binni Walter</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>MOMIGLIANO … MONTINI</t>
+          <t>BIANCHI BRUNO … BOCCONI</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -14087,12 +14621,13 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>Montagnana Mario</t>
-        </is>
-      </c>
+          <t>giusto</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>sed296|27|no|MONTAG|d9390</t>
+          <t>sed301|7|sì|BINNII|d6970</t>
         </is>
       </c>
     </row>
@@ -14104,32 +14639,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>v25</t>
+          <t>v26</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>sed296</t>
+          <t>sed301</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed296/sed296nc.pdf#page=27</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed301/sed301nc.pdf#page=7</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SUIPO</t>
+          <t>GARPANO</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Silipo Luigi</t>
+          <t>Carpano Maglioli Ernesto</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -14139,7 +14674,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SICIGNANO … SPALLICCI</t>
+          <t>CAPORALI … CARTIA</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -14157,9 +14692,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>sed296|27|no|SUIPO|d10410</t>
+          <t>sed301|7|sì|GARPANO|d11320</t>
         </is>
       </c>
     </row>
@@ -14191,12 +14727,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BINNII</t>
+          <t>RUGGIERI</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Binni Walter</t>
+          <t>Ruggeri Luigi</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -14206,7 +14742,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>BIANCHI BRUNO … BOCCONI</t>
+          <t>ROSSI MARIA MADDALENA … SACCENTI</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -14224,9 +14760,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>sed301|7|sì|BINNII|d6970</t>
+          <t>sed301|7|sì|RUGGIERI|d19820</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14780,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14258,12 +14795,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GARPANO</t>
+          <t>ANDREOILI</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carpano Maglioli Ernesto</t>
+          <t>Andreotti Giulio</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -14273,7 +14810,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>CAPORALI … CARTIA</t>
+          <t>ALDISIO … ANGELINI</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -14291,9 +14828,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>sed301|7|sì|GARPANO|d11320</t>
+          <t>sed301|7|no|ANDREOILI|d200021</t>
         </is>
       </c>
     </row>
@@ -14310,7 +14848,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14325,12 +14863,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ROCCA</t>
+          <t>ARCUNGELI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>La Rocca Vincenzo</t>
+          <t>Arcangeli Alessandro</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14340,7 +14878,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>LANDI … LEONE FRANCESCO</t>
+          <t>ARCAINI … AVANZINI</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -14358,9 +14896,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>sed301|7|sì|ROCCA|d11710</t>
+          <t>sed301|7|no|ARCUNGELI|d25310</t>
         </is>
       </c>
     </row>
@@ -14377,7 +14916,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14392,12 +14931,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RUGGIERI</t>
+          <t>CIAMPIITI</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ruggeri Luigi</t>
+          <t>Ciampitti Giovanni</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -14407,7 +14946,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ROSSI MARIA MADDALENA … SACCENTI</t>
+          <t>CHIEFFI … CICCOLUNGO</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -14425,9 +14964,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>sed301|7|sì|RUGGIERI|d19820</t>
+          <t>sed301|7|no|CIAMPIITI|d27580</t>
         </is>
       </c>
     </row>
@@ -14459,22 +14999,22 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ANDREOILI</t>
+          <t>MUURDACA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Andreotti Giulio</t>
+          <t>Murdaca Filippo</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ALDISIO … ANGELINI</t>
+          <t>MORTATI … NICOTRA MARIA</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
@@ -14492,9 +15032,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>sed301|7|no|ANDREOILI|d200021</t>
+          <t>sed301|7|no|MUURDACA|d19380</t>
         </is>
       </c>
     </row>
@@ -14511,7 +15052,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>congedo</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14526,12 +15067,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ARCUNGELI</t>
+          <t>TAMBRONI</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Arcangeli Alessandro</t>
+          <t>Tambroni Armaroli Ferdinando</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -14541,7 +15082,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ARCAINI … AVANZINI</t>
+          <t>RAVAGNAN … VANONI</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14559,9 +15100,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>sed301|7|no|ARCUNGELI|d25310</t>
+          <t>sed301|7|congedo|TAMBRONI|d12540</t>
         </is>
       </c>
     </row>
@@ -14573,32 +15115,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>v26</t>
+          <t>v27</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>sed301</t>
+          <t>sed311</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed301/sed301nc.pdf#page=7</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed311/sed311nc.pdf#page=29</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CIAMPIITI</t>
+          <t>ARGTA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ciampitti Giovanni</t>
+          <t>Arata Giuseppe</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -14608,7 +15150,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>CHIEFFI … CICCOLUNGO</t>
+          <t>AMADEI … BARBARESCHI</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr">
@@ -14626,9 +15168,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>sed301|7|no|CIAMPIITI|d27580</t>
+          <t>sed311|29|sì|ARGTA|d6480</t>
         </is>
       </c>
     </row>
@@ -14640,7 +15183,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>v26</t>
+          <t>v27</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -14650,32 +15193,32 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>sed301</t>
+          <t>sed311</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed301/sed301nc.pdf#page=7</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed311/sed311nc.pdf#page=29</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MUURDACA</t>
+          <t>VICO</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Murdaca Filippo</t>
+          <t>Vigo Gaetano</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>MORTATI … NICOTRA MARIA</t>
+          <t>VICENTINI … VILLABRUNA</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -14693,9 +15236,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>sed301|7|no|MUURDACA|d19380</t>
+          <t>sed311|29|no|VICO|d20330</t>
         </is>
       </c>
     </row>
@@ -14707,42 +15251,42 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>v26</t>
+          <t>v28</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>congedo</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>sed301</t>
+          <t>sed315</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed301/sed301nc.pdf#page=7</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed315/sed315nc.pdf#page=25</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TAMBRONI</t>
+          <t>LEONE</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tambroni Armaroli Ferdinando</t>
+          <t>Leone Francesco</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>omonimo risolto</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>RAVAGNAN … VANONI</t>
+          <t>LA ROCCA … LOMBARDI CARLO</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
@@ -14760,9 +15304,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>sed301|7|congedo|TAMBRONI|d12540</t>
+          <t>sed315|25|sì|LEONE|d8860</t>
         </is>
       </c>
     </row>
@@ -14774,32 +15319,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>v27</t>
+          <t>v28</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>sed311</t>
+          <t>sed315</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed311/sed311nc.pdf#page=29</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed315/sed315nc.pdf#page=25</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ARGTA</t>
+          <t>BETTIOT</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Arata Giuseppe</t>
+          <t>Bettiol Giuseppe Maria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -14809,7 +15354,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AMADEI … BARBARESCHI</t>
+          <t>BERTONE … BIAGIONI</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -14827,9 +15372,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>sed311|29|sì|ARGTA|d6480</t>
+          <t>sed315|25|no|BETTIOT|d17950</t>
         </is>
       </c>
     </row>
@@ -14841,7 +15387,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>v27</t>
+          <t>v28</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -14851,22 +15397,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>sed311</t>
+          <t>sed315</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed311/sed311nc.pdf#page=29</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed315/sed315nc.pdf#page=25</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>VICO</t>
+          <t>PODI</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Vigo Gaetano</t>
+          <t>Rodi Cesario</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -14876,7 +15422,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>VICENTINI … VILLABRUNA</t>
+          <t>RIVERA … RODINO UGO</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
@@ -14894,9 +15440,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>sed311|29|no|VICO|d20330</t>
+          <t>sed315|25|no|PODI|d10050</t>
         </is>
       </c>
     </row>
@@ -14913,7 +15460,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14928,22 +15475,22 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LEONE</t>
+          <t>ZIUCCARINI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Leone Francesco</t>
+          <t>Zuccarini Oliviero</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>omonimo risolto</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>LA ROCCA … LOMBARDI CARLO</t>
+          <t xml:space="preserve">ZOTTA … </t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -14961,9 +15508,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>sed315|25|sì|LEONE|d8860</t>
+          <t>sed315|25|no|ZIUCCARINI|d27120</t>
         </is>
       </c>
     </row>
@@ -14975,32 +15523,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>v28</t>
+          <t>v29</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>sed315</t>
+          <t>sed332</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed315/sed315nc.pdf#page=25</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed332/sed332nc.pdf#page=17</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BETTIOT</t>
+          <t>BAIDASSARI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bettiol Giuseppe Maria</t>
+          <t>Baldassari Gino</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -15010,7 +15558,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>BERTONE … BIAGIONI</t>
+          <t>AMADEI … BARBARESCHI</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -15028,9 +15576,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>sed315|25|no|BETTIOT|d17950</t>
+          <t>sed332|17|sì|BAIDASSARI|d6540</t>
         </is>
       </c>
     </row>
@@ -15042,42 +15591,42 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>v28</t>
+          <t>v29</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>sed315</t>
+          <t>sed332</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed315/sed315nc.pdf#page=25</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed332/sed332nc.pdf#page=17</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PODI</t>
+          <t>DUGOHI</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rodi Cesario</t>
+          <t>Dugoni Eugenio</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>RIVERA … RODINO UGO</t>
+          <t>DONATI … FANTUZZI</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -15095,9 +15644,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>sed315|25|no|PODI|d10050</t>
+          <t>sed332|17|sì|DUGOHI|d11520</t>
         </is>
       </c>
     </row>
@@ -15109,7 +15659,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>v28</t>
+          <t>v29</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -15119,22 +15669,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>sed315</t>
+          <t>sed332</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed315/sed315nc.pdf#page=25</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed332/sed332nc.pdf#page=17</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ZIUCCARINI</t>
+          <t>RERTOLA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Zuccarini Oliviero</t>
+          <t>Bertola Ermenegildo</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15144,7 +15694,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOTTA … </t>
+          <t>BENEDETTINI … BETTIOL</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -15162,9 +15712,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>sed315|25|no|ZIUCCARINI|d27120</t>
+          <t>sed332|17|no|RERTOLA|d17930</t>
         </is>
       </c>
     </row>
@@ -15181,7 +15732,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15196,22 +15747,22 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>BAIDASSARI</t>
+          <t>CARBONI</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Baldassari Gino</t>
+          <t>Carboni Enrico</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>omonimo risolto</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>AMADEI … BARBARESCHI</t>
+          <t>CARBONI ANGELO … CARIGNANI</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -15229,9 +15780,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>sed332|17|sì|BAIDASSARI|d6540</t>
+          <t>sed332|17|no|CARBONI|d27520</t>
         </is>
       </c>
     </row>
@@ -15248,7 +15800,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15263,22 +15815,22 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>DUGOHI</t>
+          <t>MASSIANI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dugoni Eugenio</t>
+          <t>Cassiani Gennaro</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>DONATI … FANTUZZI</t>
+          <t>CASO … CASTELLI EDGARDO</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
@@ -15296,9 +15848,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>sed332|17|sì|DUGOHI|d11520</t>
+          <t>sed332|17|no|MASSIANI|d18290</t>
         </is>
       </c>
     </row>
@@ -15330,12 +15883,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RERTOLA</t>
+          <t>DFAUSTO</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bertola Ermenegildo</t>
+          <t>Di Fausto Florestano</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -15345,7 +15898,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>BENEDETTINI … BETTIOL</t>
+          <t>DE VITA … DOMINEDO</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -15363,9 +15916,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>sed332|17|no|RERTOLA|d17930</t>
+          <t>sed332|17|no|DFAUSTO|d25740</t>
         </is>
       </c>
     </row>
@@ -15397,22 +15951,22 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CARBONI</t>
+          <t>FABRIANII</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carboni Enrico</t>
+          <t>Fabriani Arnaldo</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>omonimo risolto</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>CARBONI ANGELO … CARIGNANI</t>
+          <t>FABBRI … FANFANI</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
@@ -15430,9 +15984,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>sed332|17|no|CARBONI|d27520</t>
+          <t>sed332|17|no|FABRIANII|d8020</t>
         </is>
       </c>
     </row>
@@ -15464,22 +16019,22 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MASSIANI</t>
+          <t>GLACCHERO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cassiani Gennaro</t>
+          <t>Giacchero Enzo</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>fascia alfabetica</t>
+          <t>approssimato</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>CASO … CASTELLI EDGARDO</t>
+          <t>GEUNA … GIANNINI</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -15497,9 +16052,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>sed332|17|no|MASSIANI|d18290</t>
+          <t>sed332|17|no|GLACCHERO|d8500</t>
         </is>
       </c>
     </row>
@@ -15531,12 +16087,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>DFAUSTO</t>
+          <t>MANGQINI</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Di Fausto Florestano</t>
+          <t>Manzini Pierraimondo</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -15546,7 +16102,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>DE VITA … DOMINEDO</t>
+          <t>MANNIRONI … MARAZZA</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
@@ -15564,9 +16120,10 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>sed332|17|no|DFAUSTO|d25740</t>
+          <t>sed332|17|no|MANGQINI|d9030</t>
         </is>
       </c>
     </row>
@@ -15583,7 +16140,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>congedo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15598,12 +16155,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FABRIANII</t>
+          <t>LGHIDINI</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fabriani Arnaldo</t>
+          <t>Ghidini Gustavo</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -15613,7 +16170,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>FABBRI … FANFANI</t>
+          <t>CAVALLARI … JACINI</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -15631,46 +16188,47 @@
           <t>giusto</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>sed332|17|no|FABRIANII|d8020</t>
+          <t>sed332|17|congedo|LGHIDINI|d27950</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>P129</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>v29</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>sed332</t>
+          <t>sed075</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed332/sed332nc.pdf#page=17</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed075/sed075nc.pdf#page=50</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>GLACCHERO</t>
+          <t>COLONNA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Giacchero Enzo</t>
+          <t>Colonna Di Paliano Carlo</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -15680,7 +16238,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>GEUNA … GIANNINI</t>
+          <t>COLOMBO EMILIO … COLONNETTI</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -15700,54 +16258,54 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>sed332|17|no|GLACCHERO|d8500</t>
+          <t>sed075|50|sì|COLONNA|d18390</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>P130</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>v29</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sì</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>sed332</t>
+          <t>sed075</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed332/sed332nc.pdf#page=17</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed075/sed075nc.pdf#page=50</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MANGQINI</t>
+          <t>CURTO</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Manzini Pierraimondo</t>
+          <t>Del Curto Giovanni</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>approssimato</t>
+          <t>fascia alfabetica</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>MANNIRONI … MARAZZA</t>
+          <t>DE GASPERI … DELLI CASTELLI FILOMENA</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -15767,44 +16325,44 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>sed332|17|no|MANGQINI|d9030</t>
+          <t>sed075|50|sì|CURTO|d27750</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>P131</t>
+          <t>P038</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>v29</t>
+          <t>v8</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>congedo</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>sed332</t>
+          <t>sed102</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed332/sed332nc.pdf#page=17</t>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed102/sed102nc.pdf#page=16</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LGHIDINI</t>
+          <t>TAVIA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ghidini Gustavo</t>
+          <t>Taviani Paolo Emilio</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -15814,7 +16372,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>CAVALLARI … JACINI</t>
+          <t>TARGETTI … TEGA</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
@@ -15834,12 +16392,146 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>sed332|17|congedo|LGHIDINI|d27950</t>
+          <t>sed102|16|no|TAVIA|d200929</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>P045</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>v10</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>sed104</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed104/sed104nc.pdf#page=21</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>FEDE</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Federici Maria</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>fascia alfabetica</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>FANTONI … FERRARESE</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>Controlla che il nome stampato sia proprio la persona abbinata. Lascia vuoto o scegli «giusto» se lo è; altrimenti scegli «sbagliato: scarta» o scrivi «Cognome Nome» della persona giusta.</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>giusto | sbagliato: scarta | &lt;Cognome Nome&gt;</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>giusto</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>sed104|21|no|FEDE|d8120</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>P109</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>v26</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>sed301</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>https://documenti.camera.it/_dati/costituente/lavori/Assemblea/sed301/sed301nc.pdf#page=7</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ROCCA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>La Rocca Vincenzo</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>approssimato</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>LANDI … LEONE FRANCESCO</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>Controlla che il nome stampato sia proprio la persona abbinata. Lascia vuoto o scegli «giusto» se lo è; altrimenti scegli «sbagliato: scarta» o scrivi «Cognome Nome» della persona giusta.</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>giusto | sbagliato: scarta | &lt;Cognome Nome&gt;</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>giusto</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>sed301|7|sì|ROCCA|d11710</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="131">
+  <dataValidations count="133">
     <dataValidation sqref="L2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"giusto,sbagliato: scarta"</formula1>
     </dataValidation>
@@ -16231,6 +16923,12 @@
       <formula1>"giusto,sbagliato: scarta"</formula1>
     </dataValidation>
     <dataValidation sqref="L132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"giusto,sbagliato: scarta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"giusto,sbagliato: scarta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"giusto,sbagliato: scarta"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16366,6 +17064,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
